--- a/Excel-files/newlistings1.xlsx
+++ b/Excel-files/newlistings1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
   <si>
     <t>DateSelector</t>
   </si>
@@ -49,1018 +49,859 @@
     <t>MSI</t>
   </si>
   <si>
-    <t>Single Family Residence</t>
-  </si>
-  <si>
-    <t>3671</t>
-  </si>
-  <si>
-    <t>Residential Income</t>
+    <t>BONITA SPRINGS</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>ESTERO</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>FORT MYERS</t>
+  </si>
+  <si>
+    <t>1370</t>
+  </si>
+  <si>
+    <t>FORT MYERS BEACH</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>1122</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>215</t>
   </si>
   <si>
     <t>88</t>
   </si>
   <si>
-    <t>Condominium</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>Land</t>
-  </si>
-  <si>
-    <t>1558</t>
-  </si>
-  <si>
-    <t>1929</t>
-  </si>
-  <si>
-    <t>1218</t>
-  </si>
-  <si>
-    <t>3042</t>
+    <t>277</t>
+  </si>
+  <si>
+    <t>945</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>753</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>790</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>775</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>931</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>756</t>
+  </si>
+  <si>
+    <t>1353</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>970</t>
+  </si>
+  <si>
+    <t>976</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>938</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>829</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>724</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>786</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>719</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>809</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>708</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>1151</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>910</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>912</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>762</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>738</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>801</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>883</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>847</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>878</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>777</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>668</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>949</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>815</t>
+  </si>
+  <si>
+    <t>174</t>
   </si>
   <si>
     <t>81</t>
   </si>
   <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>1962</t>
-  </si>
-  <si>
-    <t>2957</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>1338</t>
-  </si>
-  <si>
-    <t>1606</t>
-  </si>
-  <si>
-    <t>2548</t>
-  </si>
-  <si>
-    <t>2346</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>1435</t>
-  </si>
-  <si>
-    <t>1047</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>1092</t>
-  </si>
-  <si>
-    <t>2189</t>
-  </si>
-  <si>
-    <t>1123</t>
-  </si>
-  <si>
-    <t>1091</t>
-  </si>
-  <si>
-    <t>2284</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>1168</t>
-  </si>
-  <si>
-    <t>1142</t>
-  </si>
-  <si>
-    <t>2333</t>
-  </si>
-  <si>
-    <t>1182</t>
-  </si>
-  <si>
-    <t>2134</t>
-  </si>
-  <si>
-    <t>1210</t>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>954</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>882</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>884</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>834</t>
+  </si>
+  <si>
+    <t>802</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>728</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>822</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>699</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>795</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>830</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>990</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>982</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>963</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>765</t>
+  </si>
+  <si>
+    <t>716</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>932</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>850</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>758</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>752</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>237</t>
   </si>
   <si>
     <t>91</t>
   </si>
   <si>
-    <t>2750</t>
-  </si>
-  <si>
-    <t>1251</t>
-  </si>
-  <si>
-    <t>1758</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>1471</t>
-  </si>
-  <si>
-    <t>2589</t>
-  </si>
-  <si>
-    <t>1714</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>1185</t>
-  </si>
-  <si>
-    <t>2175</t>
-  </si>
-  <si>
-    <t>1352</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>3567</t>
-  </si>
-  <si>
-    <t>2380</t>
-  </si>
-  <si>
-    <t>1847</t>
-  </si>
-  <si>
-    <t>2896</t>
-  </si>
-  <si>
-    <t>1772</t>
-  </si>
-  <si>
-    <t>1414</t>
-  </si>
-  <si>
-    <t>2862</t>
-  </si>
-  <si>
-    <t>1430</t>
-  </si>
-  <si>
-    <t>1741</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>2553</t>
+    <t>120</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>383</t>
+  </si>
+  <si>
+    <t>1259</t>
+  </si>
+  <si>
+    <t>1133</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>1078</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>973</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>854</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>674</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>772</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>796</t>
+  </si>
+  <si>
+    <t>180</t>
   </si>
   <si>
     <t>75</t>
   </si>
   <si>
-    <t>1342</t>
-  </si>
-  <si>
-    <t>1317</t>
-  </si>
-  <si>
-    <t>2369</t>
-  </si>
-  <si>
-    <t>1151</t>
-  </si>
-  <si>
-    <t>2098</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>972</t>
-  </si>
-  <si>
-    <t>1059</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>2135</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>1055</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>1324</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>2141</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>2740</t>
-  </si>
-  <si>
-    <t>1734</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>1571</t>
-  </si>
-  <si>
-    <t>2450</t>
-  </si>
-  <si>
-    <t>1541</t>
-  </si>
-  <si>
-    <t>1327</t>
-  </si>
-  <si>
-    <t>1257</t>
-  </si>
-  <si>
-    <t>1985</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>1599</t>
-  </si>
-  <si>
-    <t>2154</t>
-  </si>
-  <si>
-    <t>3270</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>2813</t>
-  </si>
-  <si>
-    <t>1273</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1561</t>
-  </si>
-  <si>
-    <t>2516</t>
-  </si>
-  <si>
-    <t>815</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>796</t>
-  </si>
-  <si>
-    <t>1490</t>
-  </si>
-  <si>
-    <t>2069</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>1061</t>
-  </si>
-  <si>
-    <t>1339</t>
-  </si>
-  <si>
-    <t>985</t>
-  </si>
-  <si>
-    <t>1494</t>
-  </si>
-  <si>
-    <t>2323</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>2237</t>
-  </si>
-  <si>
-    <t>1449</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>1539</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>2473</t>
-  </si>
-  <si>
-    <t>1512</t>
-  </si>
-  <si>
-    <t>2552</t>
-  </si>
-  <si>
-    <t>1447</t>
-  </si>
-  <si>
-    <t>1148</t>
-  </si>
-  <si>
-    <t>1726</t>
-  </si>
-  <si>
-    <t>2603</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>1245</t>
-  </si>
-  <si>
-    <t>1455</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>2181</t>
-  </si>
-  <si>
-    <t>1302</t>
-  </si>
-  <si>
-    <t>1930</t>
-  </si>
-  <si>
-    <t>1244</t>
-  </si>
-  <si>
-    <t>1628</t>
-  </si>
-  <si>
-    <t>2645</t>
-  </si>
-  <si>
-    <t>1846</t>
-  </si>
-  <si>
-    <t>1749</t>
-  </si>
-  <si>
-    <t>1642</t>
+    <t>759</t>
+  </si>
+  <si>
+    <t>1177</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>812</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>1513</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>1179</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>940</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>624</t>
   </si>
   <si>
     <t>84</t>
   </si>
   <si>
-    <t>2943</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>1956</t>
-  </si>
-  <si>
-    <t>2078</t>
-  </si>
-  <si>
-    <t>2746</t>
-  </si>
-  <si>
-    <t>1680</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>2663</t>
-  </si>
-  <si>
-    <t>1405</t>
-  </si>
-  <si>
-    <t>2167</t>
-  </si>
-  <si>
-    <t>1316</t>
-  </si>
-  <si>
-    <t>2485</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>2330</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>2059</t>
-  </si>
-  <si>
-    <t>1229</t>
-  </si>
-  <si>
-    <t>2355</t>
-  </si>
-  <si>
-    <t>1136</t>
-  </si>
-  <si>
-    <t>2117</t>
-  </si>
-  <si>
-    <t>1822</t>
-  </si>
-  <si>
-    <t>1099</t>
-  </si>
-  <si>
-    <t>2217</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>2469</t>
-  </si>
-  <si>
-    <t>1723</t>
-  </si>
-  <si>
-    <t>1635</t>
-  </si>
-  <si>
-    <t>2113</t>
-  </si>
-  <si>
-    <t>1139</t>
-  </si>
-  <si>
-    <t>1821</t>
-  </si>
-  <si>
-    <t>1964</t>
-  </si>
-  <si>
-    <t>2394</t>
-  </si>
-  <si>
-    <t>1459</t>
-  </si>
-  <si>
-    <t>1798</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>2491</t>
-  </si>
-  <si>
-    <t>1504</t>
-  </si>
-  <si>
-    <t>1865</t>
-  </si>
-  <si>
-    <t>3067</t>
-  </si>
-  <si>
-    <t>2139</t>
-  </si>
-  <si>
-    <t>1767</t>
-  </si>
-  <si>
-    <t>2891</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1939</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>2230</t>
-  </si>
-  <si>
-    <t>1552</t>
-  </si>
-  <si>
-    <t>2255</t>
-  </si>
-  <si>
-    <t>1252</t>
-  </si>
-  <si>
-    <t>2887</t>
-  </si>
-  <si>
-    <t>2562</t>
-  </si>
-  <si>
-    <t>1777</t>
-  </si>
-  <si>
-    <t>1035</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>2325</t>
-  </si>
-  <si>
-    <t>984</t>
-  </si>
-  <si>
-    <t>754</t>
-  </si>
-  <si>
-    <t>1799</t>
-  </si>
-  <si>
-    <t>1173</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>1750</t>
-  </si>
-  <si>
-    <t>962</t>
-  </si>
-  <si>
-    <t>867</t>
-  </si>
-  <si>
-    <t>1145</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>2177</t>
-  </si>
-  <si>
-    <t>1852</t>
-  </si>
-  <si>
-    <t>957</t>
-  </si>
-  <si>
-    <t>1432</t>
-  </si>
-  <si>
-    <t>1579</t>
-  </si>
-  <si>
-    <t>2855</t>
-  </si>
-  <si>
-    <t>1639</t>
-  </si>
-  <si>
-    <t>2724</t>
-  </si>
-  <si>
-    <t>1566</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>3144</t>
-  </si>
-  <si>
-    <t>1305</t>
-  </si>
-  <si>
-    <t>2638</t>
-  </si>
-  <si>
-    <t>1470</t>
-  </si>
-  <si>
-    <t>1469</t>
-  </si>
-  <si>
-    <t>2630</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>2520</t>
-  </si>
-  <si>
-    <t>1301</t>
-  </si>
-  <si>
-    <t>1096</t>
-  </si>
-  <si>
-    <t>2170</t>
-  </si>
-  <si>
-    <t>1131</t>
-  </si>
-  <si>
-    <t>969</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>1065</t>
-  </si>
-  <si>
-    <t>1318</t>
-  </si>
-  <si>
-    <t>1226</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2881</t>
-  </si>
-  <si>
-    <t>1362</t>
-  </si>
-  <si>
-    <t>1556</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>2718</t>
-  </si>
-  <si>
-    <t>1458</t>
-  </si>
-  <si>
-    <t>1116</t>
-  </si>
-  <si>
-    <t>2091</t>
-  </si>
-  <si>
-    <t>1193</t>
-  </si>
-  <si>
-    <t>3587</t>
-  </si>
-  <si>
-    <t>2258</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1577</t>
-  </si>
-  <si>
-    <t>3433</t>
-  </si>
-  <si>
-    <t>1421</t>
-  </si>
-  <si>
-    <t>2085</t>
-  </si>
-  <si>
-    <t>1452</t>
-  </si>
-  <si>
-    <t>3320</t>
-  </si>
-  <si>
-    <t>1837</t>
-  </si>
-  <si>
-    <t>1397</t>
-  </si>
-  <si>
-    <t>1677</t>
-  </si>
-  <si>
-    <t>3086</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>1436</t>
-  </si>
-  <si>
-    <t>2927</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>1253</t>
-  </si>
-  <si>
-    <t>1271</t>
-  </si>
-  <si>
-    <t>1051</t>
-  </si>
-  <si>
-    <t>2417</t>
-  </si>
-  <si>
-    <t>1270</t>
-  </si>
-  <si>
-    <t>2426</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>1345</t>
-  </si>
-  <si>
-    <t>1125</t>
-  </si>
-  <si>
-    <t>2537</t>
-  </si>
-  <si>
-    <t>1263</t>
-  </si>
-  <si>
-    <t>2414</t>
-  </si>
-  <si>
-    <t>1276</t>
-  </si>
-  <si>
-    <t>2541</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>1346</t>
-  </si>
-  <si>
-    <t>1026</t>
-  </si>
-  <si>
-    <t>3328</t>
-  </si>
-  <si>
-    <t>1261</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2766</t>
-  </si>
-  <si>
-    <t>1515</t>
-  </si>
-  <si>
-    <t>1115</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>4529</t>
-  </si>
-  <si>
-    <t>1747</t>
-  </si>
-  <si>
-    <t>2747</t>
-  </si>
-  <si>
-    <t>3733</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2079</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>2054</t>
-  </si>
-  <si>
-    <t>3576</t>
-  </si>
-  <si>
-    <t>1465</t>
-  </si>
-  <si>
-    <t>3150</t>
-  </si>
-  <si>
-    <t>1637</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>2869</t>
-  </si>
-  <si>
-    <t>1157</t>
-  </si>
-  <si>
-    <t>2488</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>1017</t>
-  </si>
-  <si>
-    <t>1186</t>
-  </si>
-  <si>
-    <t>1161</t>
-  </si>
-  <si>
-    <t>2390</t>
-  </si>
-  <si>
-    <t>926</t>
-  </si>
-  <si>
-    <t>2336</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>1060</t>
-  </si>
-  <si>
-    <t>1121</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>2424</t>
-  </si>
-  <si>
-    <t>3130</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>1262</t>
-  </si>
-  <si>
-    <t>2825</t>
-  </si>
-  <si>
-    <t>1732</t>
-  </si>
-  <si>
-    <t>1079</t>
-  </si>
-  <si>
-    <t>917</t>
-  </si>
-  <si>
-    <t>1337</t>
-  </si>
-  <si>
-    <t>2339</t>
-  </si>
-  <si>
-    <t>3824</t>
-  </si>
-  <si>
-    <t>2296</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>1347</t>
-  </si>
-  <si>
-    <t>1781</t>
-  </si>
-  <si>
-    <t>3229</t>
-  </si>
-  <si>
-    <t>1340</t>
-  </si>
-  <si>
-    <t>3076</t>
-  </si>
-  <si>
-    <t>1739</t>
-  </si>
-  <si>
-    <t>1178</t>
-  </si>
-  <si>
-    <t>1479</t>
-  </si>
-  <si>
-    <t>1172</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>2905</t>
+    <t>688</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>766</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>1069</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>930</t>
+  </si>
+  <si>
+    <t>873</t>
+  </si>
+  <si>
+    <t>236</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1257,7 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.57421875" customWidth="1"/>
-    <col min="2" max="2" width="23.421875" customWidth="1"/>
+    <col min="2" max="2" width="19.28125" customWidth="1"/>
     <col min="3" max="4" width="14.57421875" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" customWidth="1"/>
@@ -1562,7 +1403,7 @@
         <v>43159</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7"/>
       <c r="D7"/>
@@ -1581,7 +1422,7 @@
         <v>43159</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -1600,7 +1441,7 @@
         <v>43159</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9"/>
       <c r="D9"/>
@@ -1619,7 +1460,7 @@
         <v>43190</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10"/>
       <c r="D10"/>
@@ -1638,7 +1479,7 @@
         <v>43190</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C11"/>
       <c r="D11"/>
@@ -1657,7 +1498,7 @@
         <v>43190</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -1695,7 +1536,7 @@
         <v>43220</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14"/>
       <c r="D14"/>
@@ -1714,7 +1555,7 @@
         <v>43220</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C15"/>
       <c r="D15"/>
@@ -1733,7 +1574,7 @@
         <v>43220</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -1741,7 +1582,7 @@
       <c r="F16"/>
       <c r="G16"/>
       <c r="H16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1752,7 +1593,7 @@
         <v>43220</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C17"/>
       <c r="D17"/>
@@ -1760,7 +1601,7 @@
       <c r="F17"/>
       <c r="G17"/>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -1779,7 +1620,7 @@
       <c r="F18"/>
       <c r="G18"/>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -1790,7 +1631,7 @@
         <v>43251</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C19"/>
       <c r="D19"/>
@@ -1798,7 +1639,7 @@
       <c r="F19"/>
       <c r="G19"/>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -1809,7 +1650,7 @@
         <v>43251</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -1817,7 +1658,7 @@
       <c r="F20"/>
       <c r="G20"/>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -1828,7 +1669,7 @@
         <v>43251</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C21"/>
       <c r="D21"/>
@@ -1836,7 +1677,7 @@
       <c r="F21"/>
       <c r="G21"/>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -1847,7 +1688,7 @@
         <v>43281</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C22"/>
       <c r="D22"/>
@@ -1855,7 +1696,7 @@
       <c r="F22"/>
       <c r="G22"/>
       <c r="H22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -1866,7 +1707,7 @@
         <v>43281</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C23"/>
       <c r="D23"/>
@@ -1874,7 +1715,7 @@
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -1885,7 +1726,7 @@
         <v>43281</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C24"/>
       <c r="D24"/>
@@ -1893,7 +1734,7 @@
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -1904,7 +1745,7 @@
         <v>43281</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -1912,7 +1753,7 @@
       <c r="F25"/>
       <c r="G25"/>
       <c r="H25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -1923,7 +1764,7 @@
         <v>43312</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26"/>
       <c r="D26"/>
@@ -1931,7 +1772,7 @@
       <c r="F26"/>
       <c r="G26"/>
       <c r="H26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -1942,7 +1783,7 @@
         <v>43312</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C27"/>
       <c r="D27"/>
@@ -1950,7 +1791,7 @@
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -1961,7 +1802,7 @@
         <v>43312</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C28"/>
       <c r="D28"/>
@@ -1969,7 +1810,7 @@
       <c r="F28"/>
       <c r="G28"/>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -1988,7 +1829,7 @@
       <c r="F29"/>
       <c r="G29"/>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -2007,7 +1848,7 @@
       <c r="F30"/>
       <c r="G30"/>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -2018,7 +1859,7 @@
         <v>43343</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C31"/>
       <c r="D31"/>
@@ -2026,7 +1867,7 @@
       <c r="F31"/>
       <c r="G31"/>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -2056,7 +1897,7 @@
         <v>43343</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -2075,7 +1916,7 @@
         <v>43373</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34"/>
       <c r="D34"/>
@@ -2094,7 +1935,7 @@
         <v>43373</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C35"/>
       <c r="D35"/>
@@ -2113,7 +1954,7 @@
         <v>43373</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C36"/>
       <c r="D36"/>
@@ -2132,7 +1973,7 @@
         <v>43373</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C37"/>
       <c r="D37"/>
@@ -2189,7 +2030,7 @@
         <v>43404</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40"/>
       <c r="D40"/>
@@ -2208,7 +2049,7 @@
         <v>43404</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41"/>
       <c r="D41"/>
@@ -2227,7 +2068,7 @@
         <v>43434</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42"/>
       <c r="D42"/>
@@ -2246,7 +2087,7 @@
         <v>43434</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C43"/>
       <c r="D43"/>
@@ -2254,7 +2095,7 @@
       <c r="F43"/>
       <c r="G43"/>
       <c r="H43" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -2265,7 +2106,7 @@
         <v>43434</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C44"/>
       <c r="D44"/>
@@ -2284,7 +2125,7 @@
         <v>43434</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C45"/>
       <c r="D45"/>
@@ -2311,7 +2152,7 @@
       <c r="F46"/>
       <c r="G46"/>
       <c r="H46" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -2322,7 +2163,7 @@
         <v>43465</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C47"/>
       <c r="D47"/>
@@ -2330,7 +2171,7 @@
       <c r="F47"/>
       <c r="G47"/>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -2341,7 +2182,7 @@
         <v>43465</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C48"/>
       <c r="D48"/>
@@ -2349,7 +2190,7 @@
       <c r="F48"/>
       <c r="G48"/>
       <c r="H48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -2368,7 +2209,7 @@
       <c r="F49"/>
       <c r="G49"/>
       <c r="H49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -2379,7 +2220,7 @@
         <v>43496</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C50"/>
       <c r="D50"/>
@@ -2387,7 +2228,7 @@
       <c r="F50"/>
       <c r="G50"/>
       <c r="H50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -2398,7 +2239,7 @@
         <v>43496</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C51"/>
       <c r="D51"/>
@@ -2406,7 +2247,7 @@
       <c r="F51"/>
       <c r="G51"/>
       <c r="H51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
@@ -2417,7 +2258,7 @@
         <v>43496</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C52"/>
       <c r="D52"/>
@@ -2425,7 +2266,7 @@
       <c r="F52"/>
       <c r="G52"/>
       <c r="H52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -2444,7 +2285,7 @@
       <c r="F53"/>
       <c r="G53"/>
       <c r="H53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -2463,7 +2304,7 @@
       <c r="F54"/>
       <c r="G54"/>
       <c r="H54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -2474,7 +2315,7 @@
         <v>43524</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C55"/>
       <c r="D55"/>
@@ -2482,7 +2323,7 @@
       <c r="F55"/>
       <c r="G55"/>
       <c r="H55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -2501,7 +2342,7 @@
       <c r="F56"/>
       <c r="G56"/>
       <c r="H56" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -2512,7 +2353,7 @@
         <v>43524</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C57"/>
       <c r="D57"/>
@@ -2531,7 +2372,7 @@
         <v>43555</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C58"/>
       <c r="D58"/>
@@ -2569,7 +2410,7 @@
         <v>43555</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C60"/>
       <c r="D60"/>
@@ -2588,7 +2429,7 @@
         <v>43555</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C61"/>
       <c r="D61"/>
@@ -2607,7 +2448,7 @@
         <v>43585</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62"/>
       <c r="D62"/>
@@ -2626,7 +2467,7 @@
         <v>43585</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C63"/>
       <c r="D63"/>
@@ -2645,7 +2486,7 @@
         <v>43585</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C64"/>
       <c r="D64"/>
@@ -2664,7 +2505,7 @@
         <v>43585</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C65"/>
       <c r="D65"/>
@@ -2702,7 +2543,7 @@
         <v>43616</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C67"/>
       <c r="D67"/>
@@ -2729,7 +2570,7 @@
       <c r="F68"/>
       <c r="G68"/>
       <c r="H68" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
@@ -2740,7 +2581,7 @@
         <v>43616</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C69"/>
       <c r="D69"/>
@@ -2748,7 +2589,7 @@
       <c r="F69"/>
       <c r="G69"/>
       <c r="H69" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
@@ -2759,7 +2600,7 @@
         <v>43646</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C70"/>
       <c r="D70"/>
@@ -2767,7 +2608,7 @@
       <c r="F70"/>
       <c r="G70"/>
       <c r="H70" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
@@ -2778,7 +2619,7 @@
         <v>43646</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C71"/>
       <c r="D71"/>
@@ -2786,7 +2627,7 @@
       <c r="F71"/>
       <c r="G71"/>
       <c r="H71" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I71"/>
       <c r="J71"/>
@@ -2797,7 +2638,7 @@
         <v>43646</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C72"/>
       <c r="D72"/>
@@ -2805,7 +2646,7 @@
       <c r="F72"/>
       <c r="G72"/>
       <c r="H72" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
@@ -2816,7 +2657,7 @@
         <v>43646</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C73"/>
       <c r="D73"/>
@@ -2824,7 +2665,7 @@
       <c r="F73"/>
       <c r="G73"/>
       <c r="H73" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
@@ -2835,7 +2676,7 @@
         <v>43677</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C74"/>
       <c r="D74"/>
@@ -2843,7 +2684,7 @@
       <c r="F74"/>
       <c r="G74"/>
       <c r="H74" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
@@ -2862,7 +2703,7 @@
       <c r="F75"/>
       <c r="G75"/>
       <c r="H75" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I75"/>
       <c r="J75"/>
@@ -2881,7 +2722,7 @@
       <c r="F76"/>
       <c r="G76"/>
       <c r="H76" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I76"/>
       <c r="J76"/>
@@ -2892,7 +2733,7 @@
         <v>43677</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C77"/>
       <c r="D77"/>
@@ -2900,7 +2741,7 @@
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
@@ -2919,7 +2760,7 @@
       <c r="F78"/>
       <c r="G78"/>
       <c r="H78" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
@@ -2938,7 +2779,7 @@
       <c r="F79"/>
       <c r="G79"/>
       <c r="H79" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
@@ -2957,7 +2798,7 @@
       <c r="F80"/>
       <c r="G80"/>
       <c r="H80" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
@@ -2976,7 +2817,7 @@
       <c r="F81"/>
       <c r="G81"/>
       <c r="H81" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
@@ -2995,7 +2836,7 @@
       <c r="F82"/>
       <c r="G82"/>
       <c r="H82" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
@@ -3006,7 +2847,7 @@
         <v>43738</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C83"/>
       <c r="D83"/>
@@ -3014,7 +2855,7 @@
       <c r="F83"/>
       <c r="G83"/>
       <c r="H83" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="I83"/>
       <c r="J83"/>
@@ -3025,7 +2866,7 @@
         <v>43738</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C84"/>
       <c r="D84"/>
@@ -3033,7 +2874,7 @@
       <c r="F84"/>
       <c r="G84"/>
       <c r="H84" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I84"/>
       <c r="J84"/>
@@ -3044,7 +2885,7 @@
         <v>43738</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C85"/>
       <c r="D85"/>
@@ -3063,7 +2904,7 @@
         <v>43769</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C86"/>
       <c r="D86"/>
@@ -3090,7 +2931,7 @@
       <c r="F87"/>
       <c r="G87"/>
       <c r="H87" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="I87"/>
       <c r="J87"/>
@@ -3109,7 +2950,7 @@
       <c r="F88"/>
       <c r="G88"/>
       <c r="H88" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="I88"/>
       <c r="J88"/>
@@ -3120,7 +2961,7 @@
         <v>43769</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C89"/>
       <c r="D89"/>
@@ -3128,7 +2969,7 @@
       <c r="F89"/>
       <c r="G89"/>
       <c r="H89" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I89"/>
       <c r="J89"/>
@@ -3139,7 +2980,7 @@
         <v>43799</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C90"/>
       <c r="D90"/>
@@ -3147,7 +2988,7 @@
       <c r="F90"/>
       <c r="G90"/>
       <c r="H90" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="I90"/>
       <c r="J90"/>
@@ -3158,7 +2999,7 @@
         <v>43799</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C91"/>
       <c r="D91"/>
@@ -3166,7 +3007,7 @@
       <c r="F91"/>
       <c r="G91"/>
       <c r="H91" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I91"/>
       <c r="J91"/>
@@ -3177,7 +3018,7 @@
         <v>43799</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C92"/>
       <c r="D92"/>
@@ -3185,7 +3026,7 @@
       <c r="F92"/>
       <c r="G92"/>
       <c r="H92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I92"/>
       <c r="J92"/>
@@ -3196,7 +3037,7 @@
         <v>43799</v>
       </c>
       <c r="B93" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C93"/>
       <c r="D93"/>
@@ -3204,7 +3045,7 @@
       <c r="F93"/>
       <c r="G93"/>
       <c r="H93" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="I93"/>
       <c r="J93"/>
@@ -3215,7 +3056,7 @@
         <v>43830</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C94"/>
       <c r="D94"/>
@@ -3223,7 +3064,7 @@
       <c r="F94"/>
       <c r="G94"/>
       <c r="H94" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="I94"/>
       <c r="J94"/>
@@ -3234,7 +3075,7 @@
         <v>43830</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C95"/>
       <c r="D95"/>
@@ -3242,7 +3083,7 @@
       <c r="F95"/>
       <c r="G95"/>
       <c r="H95" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I95"/>
       <c r="J95"/>
@@ -3253,7 +3094,7 @@
         <v>43830</v>
       </c>
       <c r="B96" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C96"/>
       <c r="D96"/>
@@ -3261,7 +3102,7 @@
       <c r="F96"/>
       <c r="G96"/>
       <c r="H96" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I96"/>
       <c r="J96"/>
@@ -3272,7 +3113,7 @@
         <v>43830</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C97"/>
       <c r="D97"/>
@@ -3280,7 +3121,7 @@
       <c r="F97"/>
       <c r="G97"/>
       <c r="H97" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I97"/>
       <c r="J97"/>
@@ -3299,7 +3140,7 @@
       <c r="F98"/>
       <c r="G98"/>
       <c r="H98" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I98"/>
       <c r="J98"/>
@@ -3318,7 +3159,7 @@
       <c r="F99"/>
       <c r="G99"/>
       <c r="H99" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I99"/>
       <c r="J99"/>
@@ -3337,7 +3178,7 @@
       <c r="F100"/>
       <c r="G100"/>
       <c r="H100" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I100"/>
       <c r="J100"/>
@@ -3356,7 +3197,7 @@
       <c r="F101"/>
       <c r="G101"/>
       <c r="H101" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I101"/>
       <c r="J101"/>
@@ -3367,7 +3208,7 @@
         <v>43890</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C102"/>
       <c r="D102"/>
@@ -3375,7 +3216,7 @@
       <c r="F102"/>
       <c r="G102"/>
       <c r="H102" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I102"/>
       <c r="J102"/>
@@ -3394,7 +3235,7 @@
       <c r="F103"/>
       <c r="G103"/>
       <c r="H103" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I103"/>
       <c r="J103"/>
@@ -3405,7 +3246,7 @@
         <v>43890</v>
       </c>
       <c r="B104" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C104"/>
       <c r="D104"/>
@@ -3413,7 +3254,7 @@
       <c r="F104"/>
       <c r="G104"/>
       <c r="H104" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I104"/>
       <c r="J104"/>
@@ -3424,7 +3265,7 @@
         <v>43890</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C105"/>
       <c r="D105"/>
@@ -3432,7 +3273,7 @@
       <c r="F105"/>
       <c r="G105"/>
       <c r="H105" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I105"/>
       <c r="J105"/>
@@ -3443,7 +3284,7 @@
         <v>43921</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C106"/>
       <c r="D106"/>
@@ -3451,7 +3292,7 @@
       <c r="F106"/>
       <c r="G106"/>
       <c r="H106" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I106"/>
       <c r="J106"/>
@@ -3462,7 +3303,7 @@
         <v>43921</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C107"/>
       <c r="D107"/>
@@ -3470,7 +3311,7 @@
       <c r="F107"/>
       <c r="G107"/>
       <c r="H107" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I107"/>
       <c r="J107"/>
@@ -3481,7 +3322,7 @@
         <v>43921</v>
       </c>
       <c r="B108" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C108"/>
       <c r="D108"/>
@@ -3489,7 +3330,7 @@
       <c r="F108"/>
       <c r="G108"/>
       <c r="H108" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="I108"/>
       <c r="J108"/>
@@ -3500,7 +3341,7 @@
         <v>43921</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C109"/>
       <c r="D109"/>
@@ -3508,7 +3349,7 @@
       <c r="F109"/>
       <c r="G109"/>
       <c r="H109" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="I109"/>
       <c r="J109"/>
@@ -3519,7 +3360,7 @@
         <v>43951</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C110"/>
       <c r="D110"/>
@@ -3527,7 +3368,7 @@
       <c r="F110"/>
       <c r="G110"/>
       <c r="H110" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I110"/>
       <c r="J110"/>
@@ -3538,7 +3379,7 @@
         <v>43951</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C111"/>
       <c r="D111"/>
@@ -3546,7 +3387,7 @@
       <c r="F111"/>
       <c r="G111"/>
       <c r="H111" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I111"/>
       <c r="J111"/>
@@ -3557,7 +3398,7 @@
         <v>43951</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C112"/>
       <c r="D112"/>
@@ -3565,7 +3406,7 @@
       <c r="F112"/>
       <c r="G112"/>
       <c r="H112" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I112"/>
       <c r="J112"/>
@@ -3576,7 +3417,7 @@
         <v>43951</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C113"/>
       <c r="D113"/>
@@ -3584,7 +3425,7 @@
       <c r="F113"/>
       <c r="G113"/>
       <c r="H113" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I113"/>
       <c r="J113"/>
@@ -3595,7 +3436,7 @@
         <v>43982</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C114"/>
       <c r="D114"/>
@@ -3603,7 +3444,7 @@
       <c r="F114"/>
       <c r="G114"/>
       <c r="H114" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I114"/>
       <c r="J114"/>
@@ -3614,7 +3455,7 @@
         <v>43982</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C115"/>
       <c r="D115"/>
@@ -3622,7 +3463,7 @@
       <c r="F115"/>
       <c r="G115"/>
       <c r="H115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I115"/>
       <c r="J115"/>
@@ -3633,7 +3474,7 @@
         <v>43982</v>
       </c>
       <c r="B116" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C116"/>
       <c r="D116"/>
@@ -3641,7 +3482,7 @@
       <c r="F116"/>
       <c r="G116"/>
       <c r="H116" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I116"/>
       <c r="J116"/>
@@ -3652,7 +3493,7 @@
         <v>43982</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C117"/>
       <c r="D117"/>
@@ -3660,7 +3501,7 @@
       <c r="F117"/>
       <c r="G117"/>
       <c r="H117" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I117"/>
       <c r="J117"/>
@@ -3671,7 +3512,7 @@
         <v>44012</v>
       </c>
       <c r="B118" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C118"/>
       <c r="D118"/>
@@ -3679,7 +3520,7 @@
       <c r="F118"/>
       <c r="G118"/>
       <c r="H118" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I118"/>
       <c r="J118"/>
@@ -3690,7 +3531,7 @@
         <v>44012</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C119"/>
       <c r="D119"/>
@@ -3698,7 +3539,7 @@
       <c r="F119"/>
       <c r="G119"/>
       <c r="H119" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="I119"/>
       <c r="J119"/>
@@ -3709,7 +3550,7 @@
         <v>44012</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C120"/>
       <c r="D120"/>
@@ -3717,7 +3558,7 @@
       <c r="F120"/>
       <c r="G120"/>
       <c r="H120" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I120"/>
       <c r="J120"/>
@@ -3728,7 +3569,7 @@
         <v>44012</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C121"/>
       <c r="D121"/>
@@ -3736,7 +3577,7 @@
       <c r="F121"/>
       <c r="G121"/>
       <c r="H121" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="I121"/>
       <c r="J121"/>
@@ -3747,7 +3588,7 @@
         <v>44043</v>
       </c>
       <c r="B122" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C122"/>
       <c r="D122"/>
@@ -3755,7 +3596,7 @@
       <c r="F122"/>
       <c r="G122"/>
       <c r="H122" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="I122"/>
       <c r="J122"/>
@@ -3766,7 +3607,7 @@
         <v>44043</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C123"/>
       <c r="D123"/>
@@ -3774,7 +3615,7 @@
       <c r="F123"/>
       <c r="G123"/>
       <c r="H123" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="I123"/>
       <c r="J123"/>
@@ -3785,7 +3626,7 @@
         <v>44043</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C124"/>
       <c r="D124"/>
@@ -3793,7 +3634,7 @@
       <c r="F124"/>
       <c r="G124"/>
       <c r="H124" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="I124"/>
       <c r="J124"/>
@@ -3804,7 +3645,7 @@
         <v>44043</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125"/>
       <c r="D125"/>
@@ -3812,7 +3653,7 @@
       <c r="F125"/>
       <c r="G125"/>
       <c r="H125" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I125"/>
       <c r="J125"/>
@@ -3823,7 +3664,7 @@
         <v>44074</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C126"/>
       <c r="D126"/>
@@ -3831,7 +3672,7 @@
       <c r="F126"/>
       <c r="G126"/>
       <c r="H126" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I126"/>
       <c r="J126"/>
@@ -3850,7 +3691,7 @@
       <c r="F127"/>
       <c r="G127"/>
       <c r="H127" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I127"/>
       <c r="J127"/>
@@ -3861,7 +3702,7 @@
         <v>44074</v>
       </c>
       <c r="B128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C128"/>
       <c r="D128"/>
@@ -3869,7 +3710,7 @@
       <c r="F128"/>
       <c r="G128"/>
       <c r="H128" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I128"/>
       <c r="J128"/>
@@ -3888,7 +3729,7 @@
       <c r="F129"/>
       <c r="G129"/>
       <c r="H129" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I129"/>
       <c r="J129"/>
@@ -3899,7 +3740,7 @@
         <v>44104</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C130"/>
       <c r="D130"/>
@@ -3907,7 +3748,7 @@
       <c r="F130"/>
       <c r="G130"/>
       <c r="H130" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="I130"/>
       <c r="J130"/>
@@ -3918,7 +3759,7 @@
         <v>44104</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C131"/>
       <c r="D131"/>
@@ -3926,7 +3767,7 @@
       <c r="F131"/>
       <c r="G131"/>
       <c r="H131" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I131"/>
       <c r="J131"/>
@@ -3937,7 +3778,7 @@
         <v>44104</v>
       </c>
       <c r="B132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C132"/>
       <c r="D132"/>
@@ -3945,7 +3786,7 @@
       <c r="F132"/>
       <c r="G132"/>
       <c r="H132" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I132"/>
       <c r="J132"/>
@@ -3956,7 +3797,7 @@
         <v>44104</v>
       </c>
       <c r="B133" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C133"/>
       <c r="D133"/>
@@ -3964,7 +3805,7 @@
       <c r="F133"/>
       <c r="G133"/>
       <c r="H133" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="I133"/>
       <c r="J133"/>
@@ -3975,7 +3816,7 @@
         <v>44135</v>
       </c>
       <c r="B134" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C134"/>
       <c r="D134"/>
@@ -3983,7 +3824,7 @@
       <c r="F134"/>
       <c r="G134"/>
       <c r="H134" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I134"/>
       <c r="J134"/>
@@ -4002,7 +3843,7 @@
       <c r="F135"/>
       <c r="G135"/>
       <c r="H135" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I135"/>
       <c r="J135"/>
@@ -4013,7 +3854,7 @@
         <v>44135</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C136"/>
       <c r="D136"/>
@@ -4021,7 +3862,7 @@
       <c r="F136"/>
       <c r="G136"/>
       <c r="H136" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I136"/>
       <c r="J136"/>
@@ -4032,7 +3873,7 @@
         <v>44135</v>
       </c>
       <c r="B137" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C137"/>
       <c r="D137"/>
@@ -4040,7 +3881,7 @@
       <c r="F137"/>
       <c r="G137"/>
       <c r="H137" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I137"/>
       <c r="J137"/>
@@ -4051,7 +3892,7 @@
         <v>44165</v>
       </c>
       <c r="B138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C138"/>
       <c r="D138"/>
@@ -4059,7 +3900,7 @@
       <c r="F138"/>
       <c r="G138"/>
       <c r="H138" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I138"/>
       <c r="J138"/>
@@ -4070,7 +3911,7 @@
         <v>44165</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C139"/>
       <c r="D139"/>
@@ -4078,7 +3919,7 @@
       <c r="F139"/>
       <c r="G139"/>
       <c r="H139" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I139"/>
       <c r="J139"/>
@@ -4097,7 +3938,7 @@
       <c r="F140"/>
       <c r="G140"/>
       <c r="H140" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="I140"/>
       <c r="J140"/>
@@ -4108,7 +3949,7 @@
         <v>44165</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C141"/>
       <c r="D141"/>
@@ -4116,7 +3957,7 @@
       <c r="F141"/>
       <c r="G141"/>
       <c r="H141" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I141"/>
       <c r="J141"/>
@@ -4127,7 +3968,7 @@
         <v>44196</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C142"/>
       <c r="D142"/>
@@ -4135,7 +3976,7 @@
       <c r="F142"/>
       <c r="G142"/>
       <c r="H142" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I142"/>
       <c r="J142"/>
@@ -4146,7 +3987,7 @@
         <v>44196</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C143"/>
       <c r="D143"/>
@@ -4154,7 +3995,7 @@
       <c r="F143"/>
       <c r="G143"/>
       <c r="H143" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="I143"/>
       <c r="J143"/>
@@ -4165,7 +4006,7 @@
         <v>44196</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C144"/>
       <c r="D144"/>
@@ -4173,7 +4014,7 @@
       <c r="F144"/>
       <c r="G144"/>
       <c r="H144" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I144"/>
       <c r="J144"/>
@@ -4184,7 +4025,7 @@
         <v>44196</v>
       </c>
       <c r="B145" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C145"/>
       <c r="D145"/>
@@ -4192,7 +4033,7 @@
       <c r="F145"/>
       <c r="G145"/>
       <c r="H145" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I145"/>
       <c r="J145"/>
@@ -4203,7 +4044,7 @@
         <v>44227</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C146"/>
       <c r="D146"/>
@@ -4211,7 +4052,7 @@
       <c r="F146"/>
       <c r="G146"/>
       <c r="H146" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="I146"/>
       <c r="J146"/>
@@ -4222,7 +4063,7 @@
         <v>44227</v>
       </c>
       <c r="B147" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C147"/>
       <c r="D147"/>
@@ -4230,7 +4071,7 @@
       <c r="F147"/>
       <c r="G147"/>
       <c r="H147" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I147"/>
       <c r="J147"/>
@@ -4241,7 +4082,7 @@
         <v>44227</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C148"/>
       <c r="D148"/>
@@ -4249,7 +4090,7 @@
       <c r="F148"/>
       <c r="G148"/>
       <c r="H148" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I148"/>
       <c r="J148"/>
@@ -4260,7 +4101,7 @@
         <v>44227</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C149"/>
       <c r="D149"/>
@@ -4268,7 +4109,7 @@
       <c r="F149"/>
       <c r="G149"/>
       <c r="H149" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I149"/>
       <c r="J149"/>
@@ -4279,7 +4120,7 @@
         <v>44255</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C150"/>
       <c r="D150"/>
@@ -4287,7 +4128,7 @@
       <c r="F150"/>
       <c r="G150"/>
       <c r="H150" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I150"/>
       <c r="J150"/>
@@ -4298,7 +4139,7 @@
         <v>44255</v>
       </c>
       <c r="B151" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C151"/>
       <c r="D151"/>
@@ -4306,7 +4147,7 @@
       <c r="F151"/>
       <c r="G151"/>
       <c r="H151" t="s">
-        <v>147</v>
+        <v>57</v>
       </c>
       <c r="I151"/>
       <c r="J151"/>
@@ -4317,7 +4158,7 @@
         <v>44255</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C152"/>
       <c r="D152"/>
@@ -4325,7 +4166,7 @@
       <c r="F152"/>
       <c r="G152"/>
       <c r="H152" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I152"/>
       <c r="J152"/>
@@ -4336,7 +4177,7 @@
         <v>44255</v>
       </c>
       <c r="B153" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C153"/>
       <c r="D153"/>
@@ -4344,7 +4185,7 @@
       <c r="F153"/>
       <c r="G153"/>
       <c r="H153" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I153"/>
       <c r="J153"/>
@@ -4355,7 +4196,7 @@
         <v>44286</v>
       </c>
       <c r="B154" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C154"/>
       <c r="D154"/>
@@ -4363,7 +4204,7 @@
       <c r="F154"/>
       <c r="G154"/>
       <c r="H154" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="I154"/>
       <c r="J154"/>
@@ -4382,7 +4223,7 @@
       <c r="F155"/>
       <c r="G155"/>
       <c r="H155" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I155"/>
       <c r="J155"/>
@@ -4393,7 +4234,7 @@
         <v>44286</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C156"/>
       <c r="D156"/>
@@ -4401,7 +4242,7 @@
       <c r="F156"/>
       <c r="G156"/>
       <c r="H156" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I156"/>
       <c r="J156"/>
@@ -4412,7 +4253,7 @@
         <v>44286</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C157"/>
       <c r="D157"/>
@@ -4420,7 +4261,7 @@
       <c r="F157"/>
       <c r="G157"/>
       <c r="H157" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="I157"/>
       <c r="J157"/>
@@ -4431,7 +4272,7 @@
         <v>44316</v>
       </c>
       <c r="B158" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C158"/>
       <c r="D158"/>
@@ -4439,7 +4280,7 @@
       <c r="F158"/>
       <c r="G158"/>
       <c r="H158" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I158"/>
       <c r="J158"/>
@@ -4450,7 +4291,7 @@
         <v>44316</v>
       </c>
       <c r="B159" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C159"/>
       <c r="D159"/>
@@ -4458,7 +4299,7 @@
       <c r="F159"/>
       <c r="G159"/>
       <c r="H159" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I159"/>
       <c r="J159"/>
@@ -4469,7 +4310,7 @@
         <v>44316</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C160"/>
       <c r="D160"/>
@@ -4477,7 +4318,7 @@
       <c r="F160"/>
       <c r="G160"/>
       <c r="H160" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="I160"/>
       <c r="J160"/>
@@ -4488,7 +4329,7 @@
         <v>44316</v>
       </c>
       <c r="B161" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C161"/>
       <c r="D161"/>
@@ -4496,7 +4337,7 @@
       <c r="F161"/>
       <c r="G161"/>
       <c r="H161" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I161"/>
       <c r="J161"/>
@@ -4507,7 +4348,7 @@
         <v>44347</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C162"/>
       <c r="D162"/>
@@ -4515,7 +4356,7 @@
       <c r="F162"/>
       <c r="G162"/>
       <c r="H162" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="I162"/>
       <c r="J162"/>
@@ -4526,7 +4367,7 @@
         <v>44347</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C163"/>
       <c r="D163"/>
@@ -4534,7 +4375,7 @@
       <c r="F163"/>
       <c r="G163"/>
       <c r="H163" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I163"/>
       <c r="J163"/>
@@ -4545,7 +4386,7 @@
         <v>44347</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C164"/>
       <c r="D164"/>
@@ -4553,7 +4394,7 @@
       <c r="F164"/>
       <c r="G164"/>
       <c r="H164" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I164"/>
       <c r="J164"/>
@@ -4564,7 +4405,7 @@
         <v>44347</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C165"/>
       <c r="D165"/>
@@ -4572,7 +4413,7 @@
       <c r="F165"/>
       <c r="G165"/>
       <c r="H165" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I165"/>
       <c r="J165"/>
@@ -4591,7 +4432,7 @@
       <c r="F166"/>
       <c r="G166"/>
       <c r="H166" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I166"/>
       <c r="J166"/>
@@ -4602,7 +4443,7 @@
         <v>44377</v>
       </c>
       <c r="B167" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C167"/>
       <c r="D167"/>
@@ -4610,7 +4451,7 @@
       <c r="F167"/>
       <c r="G167"/>
       <c r="H167" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="I167"/>
       <c r="J167"/>
@@ -4621,7 +4462,7 @@
         <v>44377</v>
       </c>
       <c r="B168" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C168"/>
       <c r="D168"/>
@@ -4629,7 +4470,7 @@
       <c r="F168"/>
       <c r="G168"/>
       <c r="H168" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I168"/>
       <c r="J168"/>
@@ -4640,7 +4481,7 @@
         <v>44377</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C169"/>
       <c r="D169"/>
@@ -4648,7 +4489,7 @@
       <c r="F169"/>
       <c r="G169"/>
       <c r="H169" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I169"/>
       <c r="J169"/>
@@ -4659,7 +4500,7 @@
         <v>44408</v>
       </c>
       <c r="B170" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C170"/>
       <c r="D170"/>
@@ -4667,7 +4508,7 @@
       <c r="F170"/>
       <c r="G170"/>
       <c r="H170" t="s">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="I170"/>
       <c r="J170"/>
@@ -4678,7 +4519,7 @@
         <v>44408</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C171"/>
       <c r="D171"/>
@@ -4686,7 +4527,7 @@
       <c r="F171"/>
       <c r="G171"/>
       <c r="H171" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I171"/>
       <c r="J171"/>
@@ -4697,7 +4538,7 @@
         <v>44408</v>
       </c>
       <c r="B172" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C172"/>
       <c r="D172"/>
@@ -4705,7 +4546,7 @@
       <c r="F172"/>
       <c r="G172"/>
       <c r="H172" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I172"/>
       <c r="J172"/>
@@ -4724,7 +4565,7 @@
       <c r="F173"/>
       <c r="G173"/>
       <c r="H173" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I173"/>
       <c r="J173"/>
@@ -4735,7 +4576,7 @@
         <v>44439</v>
       </c>
       <c r="B174" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C174"/>
       <c r="D174"/>
@@ -4743,7 +4584,7 @@
       <c r="F174"/>
       <c r="G174"/>
       <c r="H174" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="I174"/>
       <c r="J174"/>
@@ -4754,7 +4595,7 @@
         <v>44439</v>
       </c>
       <c r="B175" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C175"/>
       <c r="D175"/>
@@ -4762,7 +4603,7 @@
       <c r="F175"/>
       <c r="G175"/>
       <c r="H175" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I175"/>
       <c r="J175"/>
@@ -4773,7 +4614,7 @@
         <v>44439</v>
       </c>
       <c r="B176" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C176"/>
       <c r="D176"/>
@@ -4781,7 +4622,7 @@
       <c r="F176"/>
       <c r="G176"/>
       <c r="H176" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I176"/>
       <c r="J176"/>
@@ -4792,7 +4633,7 @@
         <v>44439</v>
       </c>
       <c r="B177" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C177"/>
       <c r="D177"/>
@@ -4800,7 +4641,7 @@
       <c r="F177"/>
       <c r="G177"/>
       <c r="H177" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="I177"/>
       <c r="J177"/>
@@ -4811,7 +4652,7 @@
         <v>44469</v>
       </c>
       <c r="B178" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C178"/>
       <c r="D178"/>
@@ -4819,7 +4660,7 @@
       <c r="F178"/>
       <c r="G178"/>
       <c r="H178" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="I178"/>
       <c r="J178"/>
@@ -4838,7 +4679,7 @@
       <c r="F179"/>
       <c r="G179"/>
       <c r="H179" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I179"/>
       <c r="J179"/>
@@ -4849,7 +4690,7 @@
         <v>44469</v>
       </c>
       <c r="B180" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C180"/>
       <c r="D180"/>
@@ -4857,7 +4698,7 @@
       <c r="F180"/>
       <c r="G180"/>
       <c r="H180" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="I180"/>
       <c r="J180"/>
@@ -4868,7 +4709,7 @@
         <v>44469</v>
       </c>
       <c r="B181" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C181"/>
       <c r="D181"/>
@@ -4876,7 +4717,7 @@
       <c r="F181"/>
       <c r="G181"/>
       <c r="H181" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I181"/>
       <c r="J181"/>
@@ -4887,7 +4728,7 @@
         <v>44500</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C182"/>
       <c r="D182"/>
@@ -4895,7 +4736,7 @@
       <c r="F182"/>
       <c r="G182"/>
       <c r="H182" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="I182"/>
       <c r="J182"/>
@@ -4906,7 +4747,7 @@
         <v>44500</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C183"/>
       <c r="D183"/>
@@ -4914,7 +4755,7 @@
       <c r="F183"/>
       <c r="G183"/>
       <c r="H183" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="I183"/>
       <c r="J183"/>
@@ -4933,7 +4774,7 @@
       <c r="F184"/>
       <c r="G184"/>
       <c r="H184" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="I184"/>
       <c r="J184"/>
@@ -4944,7 +4785,7 @@
         <v>44500</v>
       </c>
       <c r="B185" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C185"/>
       <c r="D185"/>
@@ -4952,7 +4793,7 @@
       <c r="F185"/>
       <c r="G185"/>
       <c r="H185" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="I185"/>
       <c r="J185"/>
@@ -4963,7 +4804,7 @@
         <v>44530</v>
       </c>
       <c r="B186" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C186"/>
       <c r="D186"/>
@@ -4971,7 +4812,7 @@
       <c r="F186"/>
       <c r="G186"/>
       <c r="H186" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="I186"/>
       <c r="J186"/>
@@ -4982,7 +4823,7 @@
         <v>44530</v>
       </c>
       <c r="B187" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C187"/>
       <c r="D187"/>
@@ -4990,7 +4831,7 @@
       <c r="F187"/>
       <c r="G187"/>
       <c r="H187" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="I187"/>
       <c r="J187"/>
@@ -5001,7 +4842,7 @@
         <v>44530</v>
       </c>
       <c r="B188" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C188"/>
       <c r="D188"/>
@@ -5009,7 +4850,7 @@
       <c r="F188"/>
       <c r="G188"/>
       <c r="H188" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I188"/>
       <c r="J188"/>
@@ -5020,7 +4861,7 @@
         <v>44530</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C189"/>
       <c r="D189"/>
@@ -5028,7 +4869,7 @@
       <c r="F189"/>
       <c r="G189"/>
       <c r="H189" t="s">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="I189"/>
       <c r="J189"/>
@@ -5039,7 +4880,7 @@
         <v>44561</v>
       </c>
       <c r="B190" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C190"/>
       <c r="D190"/>
@@ -5047,7 +4888,7 @@
       <c r="F190"/>
       <c r="G190"/>
       <c r="H190" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I190"/>
       <c r="J190"/>
@@ -5058,7 +4899,7 @@
         <v>44561</v>
       </c>
       <c r="B191" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C191"/>
       <c r="D191"/>
@@ -5066,7 +4907,7 @@
       <c r="F191"/>
       <c r="G191"/>
       <c r="H191" t="s">
-        <v>92</v>
+        <v>173</v>
       </c>
       <c r="I191"/>
       <c r="J191"/>
@@ -5077,7 +4918,7 @@
         <v>44561</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C192"/>
       <c r="D192"/>
@@ -5085,7 +4926,7 @@
       <c r="F192"/>
       <c r="G192"/>
       <c r="H192" t="s">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="I192"/>
       <c r="J192"/>
@@ -5096,7 +4937,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C193"/>
       <c r="D193"/>
@@ -5104,7 +4945,7 @@
       <c r="F193"/>
       <c r="G193"/>
       <c r="H193" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
       <c r="I193"/>
       <c r="J193"/>
@@ -5115,7 +4956,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C194"/>
       <c r="D194"/>
@@ -5123,7 +4964,7 @@
       <c r="F194"/>
       <c r="G194"/>
       <c r="H194" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="I194"/>
       <c r="J194"/>
@@ -5134,7 +4975,7 @@
         <v>44592</v>
       </c>
       <c r="B195" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C195"/>
       <c r="D195"/>
@@ -5142,7 +4983,7 @@
       <c r="F195"/>
       <c r="G195"/>
       <c r="H195" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I195"/>
       <c r="J195"/>
@@ -5153,7 +4994,7 @@
         <v>44592</v>
       </c>
       <c r="B196" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C196"/>
       <c r="D196"/>
@@ -5161,7 +5002,7 @@
       <c r="F196"/>
       <c r="G196"/>
       <c r="H196" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="I196"/>
       <c r="J196"/>
@@ -5180,7 +5021,7 @@
       <c r="F197"/>
       <c r="G197"/>
       <c r="H197" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I197"/>
       <c r="J197"/>
@@ -5191,7 +5032,7 @@
         <v>44620</v>
       </c>
       <c r="B198" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C198"/>
       <c r="D198"/>
@@ -5199,7 +5040,7 @@
       <c r="F198"/>
       <c r="G198"/>
       <c r="H198" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I198"/>
       <c r="J198"/>
@@ -5210,7 +5051,7 @@
         <v>44620</v>
       </c>
       <c r="B199" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C199"/>
       <c r="D199"/>
@@ -5218,7 +5059,7 @@
       <c r="F199"/>
       <c r="G199"/>
       <c r="H199" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I199"/>
       <c r="J199"/>
@@ -5229,7 +5070,7 @@
         <v>44620</v>
       </c>
       <c r="B200" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C200"/>
       <c r="D200"/>
@@ -5237,7 +5078,7 @@
       <c r="F200"/>
       <c r="G200"/>
       <c r="H200" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I200"/>
       <c r="J200"/>
@@ -5248,7 +5089,7 @@
         <v>44620</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C201"/>
       <c r="D201"/>
@@ -5256,7 +5097,7 @@
       <c r="F201"/>
       <c r="G201"/>
       <c r="H201" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="I201"/>
       <c r="J201"/>
@@ -5267,7 +5108,7 @@
         <v>44651</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C202"/>
       <c r="D202"/>
@@ -5275,7 +5116,7 @@
       <c r="F202"/>
       <c r="G202"/>
       <c r="H202" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I202"/>
       <c r="J202"/>
@@ -5286,7 +5127,7 @@
         <v>44651</v>
       </c>
       <c r="B203" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C203"/>
       <c r="D203"/>
@@ -5294,7 +5135,7 @@
       <c r="F203"/>
       <c r="G203"/>
       <c r="H203" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I203"/>
       <c r="J203"/>
@@ -5305,7 +5146,7 @@
         <v>44651</v>
       </c>
       <c r="B204" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C204"/>
       <c r="D204"/>
@@ -5313,7 +5154,7 @@
       <c r="F204"/>
       <c r="G204"/>
       <c r="H204" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="I204"/>
       <c r="J204"/>
@@ -5332,7 +5173,7 @@
       <c r="F205"/>
       <c r="G205"/>
       <c r="H205" t="s">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="I205"/>
       <c r="J205"/>
@@ -5343,7 +5184,7 @@
         <v>44681</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C206"/>
       <c r="D206"/>
@@ -5351,7 +5192,7 @@
       <c r="F206"/>
       <c r="G206"/>
       <c r="H206" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I206"/>
       <c r="J206"/>
@@ -5370,7 +5211,7 @@
       <c r="F207"/>
       <c r="G207"/>
       <c r="H207" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I207"/>
       <c r="J207"/>
@@ -5381,7 +5222,7 @@
         <v>44681</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C208"/>
       <c r="D208"/>
@@ -5389,7 +5230,7 @@
       <c r="F208"/>
       <c r="G208"/>
       <c r="H208" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="I208"/>
       <c r="J208"/>
@@ -5400,7 +5241,7 @@
         <v>44681</v>
       </c>
       <c r="B209" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C209"/>
       <c r="D209"/>
@@ -5408,7 +5249,7 @@
       <c r="F209"/>
       <c r="G209"/>
       <c r="H209" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I209"/>
       <c r="J209"/>
@@ -5419,7 +5260,7 @@
         <v>44712</v>
       </c>
       <c r="B210" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C210"/>
       <c r="D210"/>
@@ -5427,7 +5268,7 @@
       <c r="F210"/>
       <c r="G210"/>
       <c r="H210" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="I210"/>
       <c r="J210"/>
@@ -5438,7 +5279,7 @@
         <v>44712</v>
       </c>
       <c r="B211" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C211"/>
       <c r="D211"/>
@@ -5446,7 +5287,7 @@
       <c r="F211"/>
       <c r="G211"/>
       <c r="H211" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="I211"/>
       <c r="J211"/>
@@ -5457,7 +5298,7 @@
         <v>44712</v>
       </c>
       <c r="B212" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C212"/>
       <c r="D212"/>
@@ -5465,7 +5306,7 @@
       <c r="F212"/>
       <c r="G212"/>
       <c r="H212" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I212"/>
       <c r="J212"/>
@@ -5476,7 +5317,7 @@
         <v>44712</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C213"/>
       <c r="D213"/>
@@ -5484,7 +5325,7 @@
       <c r="F213"/>
       <c r="G213"/>
       <c r="H213" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="I213"/>
       <c r="J213"/>
@@ -5495,7 +5336,7 @@
         <v>44742</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C214"/>
       <c r="D214"/>
@@ -5503,7 +5344,7 @@
       <c r="F214"/>
       <c r="G214"/>
       <c r="H214" t="s">
-        <v>61</v>
+        <v>192</v>
       </c>
       <c r="I214"/>
       <c r="J214"/>
@@ -5514,7 +5355,7 @@
         <v>44742</v>
       </c>
       <c r="B215" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C215"/>
       <c r="D215"/>
@@ -5522,7 +5363,7 @@
       <c r="F215"/>
       <c r="G215"/>
       <c r="H215" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="I215"/>
       <c r="J215"/>
@@ -5533,7 +5374,7 @@
         <v>44742</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C216"/>
       <c r="D216"/>
@@ -5541,7 +5382,7 @@
       <c r="F216"/>
       <c r="G216"/>
       <c r="H216" t="s">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="I216"/>
       <c r="J216"/>
@@ -5552,7 +5393,7 @@
         <v>44742</v>
       </c>
       <c r="B217" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C217"/>
       <c r="D217"/>
@@ -5560,7 +5401,7 @@
       <c r="F217"/>
       <c r="G217"/>
       <c r="H217" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="I217"/>
       <c r="J217"/>
@@ -5579,7 +5420,7 @@
       <c r="F218"/>
       <c r="G218"/>
       <c r="H218" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="I218"/>
       <c r="J218"/>
@@ -5590,7 +5431,7 @@
         <v>44773</v>
       </c>
       <c r="B219" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C219"/>
       <c r="D219"/>
@@ -5598,7 +5439,7 @@
       <c r="F219"/>
       <c r="G219"/>
       <c r="H219" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="I219"/>
       <c r="J219"/>
@@ -5609,7 +5450,7 @@
         <v>44773</v>
       </c>
       <c r="B220" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C220"/>
       <c r="D220"/>
@@ -5617,7 +5458,7 @@
       <c r="F220"/>
       <c r="G220"/>
       <c r="H220" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="I220"/>
       <c r="J220"/>
@@ -5628,7 +5469,7 @@
         <v>44773</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C221"/>
       <c r="D221"/>
@@ -5636,7 +5477,7 @@
       <c r="F221"/>
       <c r="G221"/>
       <c r="H221" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="I221"/>
       <c r="J221"/>
@@ -5647,7 +5488,7 @@
         <v>44804</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C222"/>
       <c r="D222"/>
@@ -5655,7 +5496,7 @@
       <c r="F222"/>
       <c r="G222"/>
       <c r="H222" t="s">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="I222"/>
       <c r="J222"/>
@@ -5666,7 +5507,7 @@
         <v>44804</v>
       </c>
       <c r="B223" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C223"/>
       <c r="D223"/>
@@ -5674,7 +5515,7 @@
       <c r="F223"/>
       <c r="G223"/>
       <c r="H223" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I223"/>
       <c r="J223"/>
@@ -5685,7 +5526,7 @@
         <v>44804</v>
       </c>
       <c r="B224" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C224"/>
       <c r="D224"/>
@@ -5693,7 +5534,7 @@
       <c r="F224"/>
       <c r="G224"/>
       <c r="H224" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="I224"/>
       <c r="J224"/>
@@ -5704,7 +5545,7 @@
         <v>44804</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C225"/>
       <c r="D225"/>
@@ -5712,7 +5553,7 @@
       <c r="F225"/>
       <c r="G225"/>
       <c r="H225" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="I225"/>
       <c r="J225"/>
@@ -5723,7 +5564,7 @@
         <v>44834</v>
       </c>
       <c r="B226" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C226"/>
       <c r="D226"/>
@@ -5731,7 +5572,7 @@
       <c r="F226"/>
       <c r="G226"/>
       <c r="H226" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="I226"/>
       <c r="J226"/>
@@ -5742,7 +5583,7 @@
         <v>44834</v>
       </c>
       <c r="B227" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C227"/>
       <c r="D227"/>
@@ -5750,7 +5591,7 @@
       <c r="F227"/>
       <c r="G227"/>
       <c r="H227" t="s">
-        <v>210</v>
+        <v>132</v>
       </c>
       <c r="I227"/>
       <c r="J227"/>
@@ -5769,7 +5610,7 @@
       <c r="F228"/>
       <c r="G228"/>
       <c r="H228" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="I228"/>
       <c r="J228"/>
@@ -5780,7 +5621,7 @@
         <v>44834</v>
       </c>
       <c r="B229" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C229"/>
       <c r="D229"/>
@@ -5788,7 +5629,7 @@
       <c r="F229"/>
       <c r="G229"/>
       <c r="H229" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="I229"/>
       <c r="J229"/>
@@ -5807,7 +5648,7 @@
       <c r="F230"/>
       <c r="G230"/>
       <c r="H230" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="I230"/>
       <c r="J230"/>
@@ -5826,7 +5667,7 @@
       <c r="F231"/>
       <c r="G231"/>
       <c r="H231" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="I231"/>
       <c r="J231"/>
@@ -5845,7 +5686,7 @@
       <c r="F232"/>
       <c r="G232"/>
       <c r="H232" t="s">
-        <v>215</v>
+        <v>32</v>
       </c>
       <c r="I232"/>
       <c r="J232"/>
@@ -5864,7 +5705,7 @@
       <c r="F233"/>
       <c r="G233"/>
       <c r="H233" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="I233"/>
       <c r="J233"/>
@@ -5875,7 +5716,7 @@
         <v>44895</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C234"/>
       <c r="D234"/>
@@ -5883,7 +5724,7 @@
       <c r="F234"/>
       <c r="G234"/>
       <c r="H234" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="I234"/>
       <c r="J234"/>
@@ -5894,7 +5735,7 @@
         <v>44895</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C235"/>
       <c r="D235"/>
@@ -5902,7 +5743,7 @@
       <c r="F235"/>
       <c r="G235"/>
       <c r="H235" t="s">
-        <v>218</v>
+        <v>66</v>
       </c>
       <c r="I235"/>
       <c r="J235"/>
@@ -5913,7 +5754,7 @@
         <v>44895</v>
       </c>
       <c r="B236" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C236"/>
       <c r="D236"/>
@@ -5921,7 +5762,7 @@
       <c r="F236"/>
       <c r="G236"/>
       <c r="H236" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="I236"/>
       <c r="J236"/>
@@ -5940,7 +5781,7 @@
       <c r="F237"/>
       <c r="G237"/>
       <c r="H237" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="I237"/>
       <c r="J237"/>
@@ -5951,7 +5792,7 @@
         <v>44926</v>
       </c>
       <c r="B238" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C238"/>
       <c r="D238"/>
@@ -5959,7 +5800,7 @@
       <c r="F238"/>
       <c r="G238"/>
       <c r="H238" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="I238"/>
       <c r="J238"/>
@@ -5970,7 +5811,7 @@
         <v>44926</v>
       </c>
       <c r="B239" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C239"/>
       <c r="D239"/>
@@ -5978,7 +5819,7 @@
       <c r="F239"/>
       <c r="G239"/>
       <c r="H239" t="s">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="I239"/>
       <c r="J239"/>
@@ -5989,7 +5830,7 @@
         <v>44926</v>
       </c>
       <c r="B240" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C240"/>
       <c r="D240"/>
@@ -5997,7 +5838,7 @@
       <c r="F240"/>
       <c r="G240"/>
       <c r="H240" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="I240"/>
       <c r="J240"/>
@@ -6008,7 +5849,7 @@
         <v>44926</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C241"/>
       <c r="D241"/>
@@ -6027,7 +5868,7 @@
         <v>44957</v>
       </c>
       <c r="B242" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C242"/>
       <c r="D242"/>
@@ -6035,7 +5876,7 @@
       <c r="F242"/>
       <c r="G242"/>
       <c r="H242" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="I242"/>
       <c r="J242"/>
@@ -6054,7 +5895,7 @@
       <c r="F243"/>
       <c r="G243"/>
       <c r="H243" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="I243"/>
       <c r="J243"/>
@@ -6065,7 +5906,7 @@
         <v>44957</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C244"/>
       <c r="D244"/>
@@ -6073,7 +5914,7 @@
       <c r="F244"/>
       <c r="G244"/>
       <c r="H244" t="s">
-        <v>223</v>
+        <v>99</v>
       </c>
       <c r="I244"/>
       <c r="J244"/>
@@ -6084,7 +5925,7 @@
         <v>44957</v>
       </c>
       <c r="B245" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C245"/>
       <c r="D245"/>
@@ -6092,7 +5933,7 @@
       <c r="F245"/>
       <c r="G245"/>
       <c r="H245" t="s">
-        <v>224</v>
+        <v>140</v>
       </c>
       <c r="I245"/>
       <c r="J245"/>
@@ -6103,7 +5944,7 @@
         <v>44985</v>
       </c>
       <c r="B246" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C246"/>
       <c r="D246"/>
@@ -6111,7 +5952,7 @@
       <c r="F246"/>
       <c r="G246"/>
       <c r="H246" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="I246"/>
       <c r="J246"/>
@@ -6122,7 +5963,7 @@
         <v>44985</v>
       </c>
       <c r="B247" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C247"/>
       <c r="D247"/>
@@ -6130,7 +5971,7 @@
       <c r="F247"/>
       <c r="G247"/>
       <c r="H247" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="I247"/>
       <c r="J247"/>
@@ -6141,7 +5982,7 @@
         <v>44985</v>
       </c>
       <c r="B248" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C248"/>
       <c r="D248"/>
@@ -6149,7 +5990,7 @@
       <c r="F248"/>
       <c r="G248"/>
       <c r="H248" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="I248"/>
       <c r="J248"/>
@@ -6168,7 +6009,7 @@
       <c r="F249"/>
       <c r="G249"/>
       <c r="H249" t="s">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="I249"/>
       <c r="J249"/>
@@ -6179,7 +6020,7 @@
         <v>45016</v>
       </c>
       <c r="B250" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C250"/>
       <c r="D250"/>
@@ -6187,7 +6028,7 @@
       <c r="F250"/>
       <c r="G250"/>
       <c r="H250" t="s">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="I250"/>
       <c r="J250"/>
@@ -6198,7 +6039,7 @@
         <v>45016</v>
       </c>
       <c r="B251" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C251"/>
       <c r="D251"/>
@@ -6206,7 +6047,7 @@
       <c r="F251"/>
       <c r="G251"/>
       <c r="H251" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="I251"/>
       <c r="J251"/>
@@ -6217,7 +6058,7 @@
         <v>45016</v>
       </c>
       <c r="B252" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C252"/>
       <c r="D252"/>
@@ -6225,7 +6066,7 @@
       <c r="F252"/>
       <c r="G252"/>
       <c r="H252" t="s">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="I252"/>
       <c r="J252"/>
@@ -6236,7 +6077,7 @@
         <v>45016</v>
       </c>
       <c r="B253" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C253"/>
       <c r="D253"/>
@@ -6244,7 +6085,7 @@
       <c r="F253"/>
       <c r="G253"/>
       <c r="H253" t="s">
-        <v>229</v>
+        <v>23</v>
       </c>
       <c r="I253"/>
       <c r="J253"/>
@@ -6255,7 +6096,7 @@
         <v>45046</v>
       </c>
       <c r="B254" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C254"/>
       <c r="D254"/>
@@ -6263,7 +6104,7 @@
       <c r="F254"/>
       <c r="G254"/>
       <c r="H254" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="I254"/>
       <c r="J254"/>
@@ -6282,7 +6123,7 @@
       <c r="F255"/>
       <c r="G255"/>
       <c r="H255" t="s">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="I255"/>
       <c r="J255"/>
@@ -6293,7 +6134,7 @@
         <v>45046</v>
       </c>
       <c r="B256" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C256"/>
       <c r="D256"/>
@@ -6301,7 +6142,7 @@
       <c r="F256"/>
       <c r="G256"/>
       <c r="H256" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="I256"/>
       <c r="J256"/>
@@ -6312,7 +6153,7 @@
         <v>45046</v>
       </c>
       <c r="B257" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C257"/>
       <c r="D257"/>
@@ -6320,7 +6161,7 @@
       <c r="F257"/>
       <c r="G257"/>
       <c r="H257" t="s">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="I257"/>
       <c r="J257"/>
@@ -6339,7 +6180,7 @@
       <c r="F258"/>
       <c r="G258"/>
       <c r="H258" t="s">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="I258"/>
       <c r="J258"/>
@@ -6350,7 +6191,7 @@
         <v>45077</v>
       </c>
       <c r="B259" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C259"/>
       <c r="D259"/>
@@ -6358,7 +6199,7 @@
       <c r="F259"/>
       <c r="G259"/>
       <c r="H259" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="I259"/>
       <c r="J259"/>
@@ -6369,7 +6210,7 @@
         <v>45077</v>
       </c>
       <c r="B260" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C260"/>
       <c r="D260"/>
@@ -6377,7 +6218,7 @@
       <c r="F260"/>
       <c r="G260"/>
       <c r="H260" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="I260"/>
       <c r="J260"/>
@@ -6396,7 +6237,7 @@
       <c r="F261"/>
       <c r="G261"/>
       <c r="H261" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="I261"/>
       <c r="J261"/>
@@ -6407,7 +6248,7 @@
         <v>45107</v>
       </c>
       <c r="B262" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C262"/>
       <c r="D262"/>
@@ -6415,7 +6256,7 @@
       <c r="F262"/>
       <c r="G262"/>
       <c r="H262" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="I262"/>
       <c r="J262"/>
@@ -6426,7 +6267,7 @@
         <v>45107</v>
       </c>
       <c r="B263" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C263"/>
       <c r="D263"/>
@@ -6434,7 +6275,7 @@
       <c r="F263"/>
       <c r="G263"/>
       <c r="H263" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="I263"/>
       <c r="J263"/>
@@ -6445,7 +6286,7 @@
         <v>45107</v>
       </c>
       <c r="B264" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C264"/>
       <c r="D264"/>
@@ -6453,7 +6294,7 @@
       <c r="F264"/>
       <c r="G264"/>
       <c r="H264" t="s">
-        <v>237</v>
+        <v>47</v>
       </c>
       <c r="I264"/>
       <c r="J264"/>
@@ -6464,7 +6305,7 @@
         <v>45107</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C265"/>
       <c r="D265"/>
@@ -6472,7 +6313,7 @@
       <c r="F265"/>
       <c r="G265"/>
       <c r="H265" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I265"/>
       <c r="J265"/>
@@ -6483,7 +6324,7 @@
         <v>45138</v>
       </c>
       <c r="B266" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C266"/>
       <c r="D266"/>
@@ -6491,7 +6332,7 @@
       <c r="F266"/>
       <c r="G266"/>
       <c r="H266" t="s">
-        <v>239</v>
+        <v>105</v>
       </c>
       <c r="I266"/>
       <c r="J266"/>
@@ -6510,7 +6351,7 @@
       <c r="F267"/>
       <c r="G267"/>
       <c r="H267" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="I267"/>
       <c r="J267"/>
@@ -6521,7 +6362,7 @@
         <v>45138</v>
       </c>
       <c r="B268" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C268"/>
       <c r="D268"/>
@@ -6529,7 +6370,7 @@
       <c r="F268"/>
       <c r="G268"/>
       <c r="H268" t="s">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="I268"/>
       <c r="J268"/>
@@ -6540,7 +6381,7 @@
         <v>45138</v>
       </c>
       <c r="B269" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C269"/>
       <c r="D269"/>
@@ -6548,7 +6389,7 @@
       <c r="F269"/>
       <c r="G269"/>
       <c r="H269" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="I269"/>
       <c r="J269"/>
@@ -6559,7 +6400,7 @@
         <v>45169</v>
       </c>
       <c r="B270" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C270"/>
       <c r="D270"/>
@@ -6567,7 +6408,7 @@
       <c r="F270"/>
       <c r="G270"/>
       <c r="H270" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="I270"/>
       <c r="J270"/>
@@ -6578,7 +6419,7 @@
         <v>45169</v>
       </c>
       <c r="B271" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C271"/>
       <c r="D271"/>
@@ -6586,7 +6427,7 @@
       <c r="F271"/>
       <c r="G271"/>
       <c r="H271" t="s">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="I271"/>
       <c r="J271"/>
@@ -6597,7 +6438,7 @@
         <v>45169</v>
       </c>
       <c r="B272" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C272"/>
       <c r="D272"/>
@@ -6605,7 +6446,7 @@
       <c r="F272"/>
       <c r="G272"/>
       <c r="H272" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="I272"/>
       <c r="J272"/>
@@ -6616,7 +6457,7 @@
         <v>45169</v>
       </c>
       <c r="B273" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C273"/>
       <c r="D273"/>
@@ -6624,7 +6465,7 @@
       <c r="F273"/>
       <c r="G273"/>
       <c r="H273" t="s">
-        <v>99</v>
+        <v>224</v>
       </c>
       <c r="I273"/>
       <c r="J273"/>
@@ -6635,7 +6476,7 @@
         <v>45199</v>
       </c>
       <c r="B274" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C274"/>
       <c r="D274"/>
@@ -6643,7 +6484,7 @@
       <c r="F274"/>
       <c r="G274"/>
       <c r="H274" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="I274"/>
       <c r="J274"/>
@@ -6654,7 +6495,7 @@
         <v>45199</v>
       </c>
       <c r="B275" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C275"/>
       <c r="D275"/>
@@ -6662,7 +6503,7 @@
       <c r="F275"/>
       <c r="G275"/>
       <c r="H275" t="s">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="I275"/>
       <c r="J275"/>
@@ -6673,7 +6514,7 @@
         <v>45199</v>
       </c>
       <c r="B276" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C276"/>
       <c r="D276"/>
@@ -6681,7 +6522,7 @@
       <c r="F276"/>
       <c r="G276"/>
       <c r="H276" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="I276"/>
       <c r="J276"/>
@@ -6692,7 +6533,7 @@
         <v>45199</v>
       </c>
       <c r="B277" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C277"/>
       <c r="D277"/>
@@ -6700,7 +6541,7 @@
       <c r="F277"/>
       <c r="G277"/>
       <c r="H277" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="I277"/>
       <c r="J277"/>
@@ -6719,7 +6560,7 @@
       <c r="F278"/>
       <c r="G278"/>
       <c r="H278" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="I278"/>
       <c r="J278"/>
@@ -6730,7 +6571,7 @@
         <v>45230</v>
       </c>
       <c r="B279" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C279"/>
       <c r="D279"/>
@@ -6738,7 +6579,7 @@
       <c r="F279"/>
       <c r="G279"/>
       <c r="H279" t="s">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="I279"/>
       <c r="J279"/>
@@ -6749,7 +6590,7 @@
         <v>45230</v>
       </c>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C280"/>
       <c r="D280"/>
@@ -6757,7 +6598,7 @@
       <c r="F280"/>
       <c r="G280"/>
       <c r="H280" t="s">
-        <v>249</v>
+        <v>93</v>
       </c>
       <c r="I280"/>
       <c r="J280"/>
@@ -6776,7 +6617,7 @@
       <c r="F281"/>
       <c r="G281"/>
       <c r="H281" t="s">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="I281"/>
       <c r="J281"/>
@@ -6787,7 +6628,7 @@
         <v>45260</v>
       </c>
       <c r="B282" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C282"/>
       <c r="D282"/>
@@ -6795,7 +6636,7 @@
       <c r="F282"/>
       <c r="G282"/>
       <c r="H282" t="s">
-        <v>251</v>
+        <v>85</v>
       </c>
       <c r="I282"/>
       <c r="J282"/>
@@ -6806,7 +6647,7 @@
         <v>45260</v>
       </c>
       <c r="B283" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C283"/>
       <c r="D283"/>
@@ -6814,7 +6655,7 @@
       <c r="F283"/>
       <c r="G283"/>
       <c r="H283" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="I283"/>
       <c r="J283"/>
@@ -6825,7 +6666,7 @@
         <v>45260</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C284"/>
       <c r="D284"/>
@@ -6833,7 +6674,7 @@
       <c r="F284"/>
       <c r="G284"/>
       <c r="H284" t="s">
-        <v>252</v>
+        <v>70</v>
       </c>
       <c r="I284"/>
       <c r="J284"/>
@@ -6844,7 +6685,7 @@
         <v>45260</v>
       </c>
       <c r="B285" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C285"/>
       <c r="D285"/>
@@ -6852,7 +6693,7 @@
       <c r="F285"/>
       <c r="G285"/>
       <c r="H285" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="I285"/>
       <c r="J285"/>
@@ -6871,7 +6712,7 @@
       <c r="F286"/>
       <c r="G286"/>
       <c r="H286" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="I286"/>
       <c r="J286"/>
@@ -6882,7 +6723,7 @@
         <v>45291</v>
       </c>
       <c r="B287" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C287"/>
       <c r="D287"/>
@@ -6890,7 +6731,7 @@
       <c r="F287"/>
       <c r="G287"/>
       <c r="H287" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="I287"/>
       <c r="J287"/>
@@ -6909,7 +6750,7 @@
       <c r="F288"/>
       <c r="G288"/>
       <c r="H288" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="I288"/>
       <c r="J288"/>
@@ -6920,7 +6761,7 @@
         <v>45291</v>
       </c>
       <c r="B289" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C289"/>
       <c r="D289"/>
@@ -6928,7 +6769,7 @@
       <c r="F289"/>
       <c r="G289"/>
       <c r="H289" t="s">
-        <v>102</v>
+        <v>233</v>
       </c>
       <c r="I289"/>
       <c r="J289"/>
@@ -6939,7 +6780,7 @@
         <v>45322</v>
       </c>
       <c r="B290" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C290"/>
       <c r="D290"/>
@@ -6947,7 +6788,7 @@
       <c r="F290"/>
       <c r="G290"/>
       <c r="H290" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="I290"/>
       <c r="J290"/>
@@ -6958,7 +6799,7 @@
         <v>45322</v>
       </c>
       <c r="B291" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C291"/>
       <c r="D291"/>
@@ -6966,7 +6807,7 @@
       <c r="F291"/>
       <c r="G291"/>
       <c r="H291" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="I291"/>
       <c r="J291"/>
@@ -6977,7 +6818,7 @@
         <v>45322</v>
       </c>
       <c r="B292" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C292"/>
       <c r="D292"/>
@@ -6985,7 +6826,7 @@
       <c r="F292"/>
       <c r="G292"/>
       <c r="H292" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="I292"/>
       <c r="J292"/>
@@ -6996,7 +6837,7 @@
         <v>45322</v>
       </c>
       <c r="B293" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C293"/>
       <c r="D293"/>
@@ -7004,7 +6845,7 @@
       <c r="F293"/>
       <c r="G293"/>
       <c r="H293" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="I293"/>
       <c r="J293"/>
@@ -7015,7 +6856,7 @@
         <v>45351</v>
       </c>
       <c r="B294" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C294"/>
       <c r="D294"/>
@@ -7023,7 +6864,7 @@
       <c r="F294"/>
       <c r="G294"/>
       <c r="H294" t="s">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="I294"/>
       <c r="J294"/>
@@ -7034,7 +6875,7 @@
         <v>45351</v>
       </c>
       <c r="B295" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C295"/>
       <c r="D295"/>
@@ -7042,7 +6883,7 @@
       <c r="F295"/>
       <c r="G295"/>
       <c r="H295" t="s">
-        <v>136</v>
+        <v>238</v>
       </c>
       <c r="I295"/>
       <c r="J295"/>
@@ -7053,7 +6894,7 @@
         <v>45351</v>
       </c>
       <c r="B296" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C296"/>
       <c r="D296"/>
@@ -7061,7 +6902,7 @@
       <c r="F296"/>
       <c r="G296"/>
       <c r="H296" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="I296"/>
       <c r="J296"/>
@@ -7072,7 +6913,7 @@
         <v>45351</v>
       </c>
       <c r="B297" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C297"/>
       <c r="D297"/>
@@ -7080,7 +6921,7 @@
       <c r="F297"/>
       <c r="G297"/>
       <c r="H297" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="I297"/>
       <c r="J297"/>
@@ -7091,7 +6932,7 @@
         <v>45382</v>
       </c>
       <c r="B298" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C298"/>
       <c r="D298"/>
@@ -7099,7 +6940,7 @@
       <c r="F298"/>
       <c r="G298"/>
       <c r="H298" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="I298"/>
       <c r="J298"/>
@@ -7118,7 +6959,7 @@
       <c r="F299"/>
       <c r="G299"/>
       <c r="H299" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="I299"/>
       <c r="J299"/>
@@ -7137,7 +6978,7 @@
       <c r="F300"/>
       <c r="G300"/>
       <c r="H300" t="s">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="I300"/>
       <c r="J300"/>
@@ -7148,7 +6989,7 @@
         <v>45382</v>
       </c>
       <c r="B301" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C301"/>
       <c r="D301"/>
@@ -7156,7 +6997,7 @@
       <c r="F301"/>
       <c r="G301"/>
       <c r="H301" t="s">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="I301"/>
       <c r="J301"/>
@@ -7167,7 +7008,7 @@
         <v>45412</v>
       </c>
       <c r="B302" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C302"/>
       <c r="D302"/>
@@ -7175,7 +7016,7 @@
       <c r="F302"/>
       <c r="G302"/>
       <c r="H302" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="I302"/>
       <c r="J302"/>
@@ -7186,7 +7027,7 @@
         <v>45412</v>
       </c>
       <c r="B303" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C303"/>
       <c r="D303"/>
@@ -7194,7 +7035,7 @@
       <c r="F303"/>
       <c r="G303"/>
       <c r="H303" t="s">
-        <v>267</v>
+        <v>14</v>
       </c>
       <c r="I303"/>
       <c r="J303"/>
@@ -7205,7 +7046,7 @@
         <v>45412</v>
       </c>
       <c r="B304" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C304"/>
       <c r="D304"/>
@@ -7213,7 +7054,7 @@
       <c r="F304"/>
       <c r="G304"/>
       <c r="H304" t="s">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c r="I304"/>
       <c r="J304"/>
@@ -7232,7 +7073,7 @@
       <c r="F305"/>
       <c r="G305"/>
       <c r="H305" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="I305"/>
       <c r="J305"/>
@@ -7243,7 +7084,7 @@
         <v>45443</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C306"/>
       <c r="D306"/>
@@ -7251,7 +7092,7 @@
       <c r="F306"/>
       <c r="G306"/>
       <c r="H306" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="I306"/>
       <c r="J306"/>
@@ -7270,7 +7111,7 @@
       <c r="F307"/>
       <c r="G307"/>
       <c r="H307" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="I307"/>
       <c r="J307"/>
@@ -7281,7 +7122,7 @@
         <v>45443</v>
       </c>
       <c r="B308" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C308"/>
       <c r="D308"/>
@@ -7289,7 +7130,7 @@
       <c r="F308"/>
       <c r="G308"/>
       <c r="H308" t="s">
-        <v>272</v>
+        <v>172</v>
       </c>
       <c r="I308"/>
       <c r="J308"/>
@@ -7300,7 +7141,7 @@
         <v>45443</v>
       </c>
       <c r="B309" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C309"/>
       <c r="D309"/>
@@ -7308,7 +7149,7 @@
       <c r="F309"/>
       <c r="G309"/>
       <c r="H309" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="I309"/>
       <c r="J309"/>
@@ -7319,7 +7160,7 @@
         <v>45473</v>
       </c>
       <c r="B310" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C310"/>
       <c r="D310"/>
@@ -7327,7 +7168,7 @@
       <c r="F310"/>
       <c r="G310"/>
       <c r="H310" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="I310"/>
       <c r="J310"/>
@@ -7338,7 +7179,7 @@
         <v>45473</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C311"/>
       <c r="D311"/>
@@ -7346,7 +7187,7 @@
       <c r="F311"/>
       <c r="G311"/>
       <c r="H311" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="I311"/>
       <c r="J311"/>
@@ -7365,7 +7206,7 @@
       <c r="F312"/>
       <c r="G312"/>
       <c r="H312" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="I312"/>
       <c r="J312"/>
@@ -7376,7 +7217,7 @@
         <v>45473</v>
       </c>
       <c r="B313" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C313"/>
       <c r="D313"/>
@@ -7384,7 +7225,7 @@
       <c r="F313"/>
       <c r="G313"/>
       <c r="H313" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="I313"/>
       <c r="J313"/>
@@ -7395,7 +7236,7 @@
         <v>45504</v>
       </c>
       <c r="B314" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C314"/>
       <c r="D314"/>
@@ -7403,7 +7244,7 @@
       <c r="F314"/>
       <c r="G314"/>
       <c r="H314" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="I314"/>
       <c r="J314"/>
@@ -7422,7 +7263,7 @@
       <c r="F315"/>
       <c r="G315"/>
       <c r="H315" t="s">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="I315"/>
       <c r="J315"/>
@@ -7441,7 +7282,7 @@
       <c r="F316"/>
       <c r="G316"/>
       <c r="H316" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="I316"/>
       <c r="J316"/>
@@ -7452,7 +7293,7 @@
         <v>45504</v>
       </c>
       <c r="B317" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C317"/>
       <c r="D317"/>
@@ -7460,7 +7301,7 @@
       <c r="F317"/>
       <c r="G317"/>
       <c r="H317" t="s">
-        <v>279</v>
+        <v>58</v>
       </c>
       <c r="I317"/>
       <c r="J317"/>
@@ -7471,7 +7312,7 @@
         <v>45535</v>
       </c>
       <c r="B318" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C318"/>
       <c r="D318"/>
@@ -7479,7 +7320,7 @@
       <c r="F318"/>
       <c r="G318"/>
       <c r="H318" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="I318"/>
       <c r="J318"/>
@@ -7490,7 +7331,7 @@
         <v>45535</v>
       </c>
       <c r="B319" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C319"/>
       <c r="D319"/>
@@ -7498,7 +7339,7 @@
       <c r="F319"/>
       <c r="G319"/>
       <c r="H319" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="I319"/>
       <c r="J319"/>
@@ -7509,7 +7350,7 @@
         <v>45535</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C320"/>
       <c r="D320"/>
@@ -7517,7 +7358,7 @@
       <c r="F320"/>
       <c r="G320"/>
       <c r="H320" t="s">
-        <v>281</v>
+        <v>32</v>
       </c>
       <c r="I320"/>
       <c r="J320"/>
@@ -7528,7 +7369,7 @@
         <v>45535</v>
       </c>
       <c r="B321" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C321"/>
       <c r="D321"/>
@@ -7536,7 +7377,7 @@
       <c r="F321"/>
       <c r="G321"/>
       <c r="H321" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="I321"/>
       <c r="J321"/>
@@ -7547,7 +7388,7 @@
         <v>45565</v>
       </c>
       <c r="B322" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C322"/>
       <c r="D322"/>
@@ -7555,7 +7396,7 @@
       <c r="F322"/>
       <c r="G322"/>
       <c r="H322" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I322"/>
       <c r="J322"/>
@@ -7566,7 +7407,7 @@
         <v>45565</v>
       </c>
       <c r="B323" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C323"/>
       <c r="D323"/>
@@ -7574,7 +7415,7 @@
       <c r="F323"/>
       <c r="G323"/>
       <c r="H323" t="s">
-        <v>283</v>
+        <v>45</v>
       </c>
       <c r="I323"/>
       <c r="J323"/>
@@ -7593,7 +7434,7 @@
       <c r="F324"/>
       <c r="G324"/>
       <c r="H324" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="I324"/>
       <c r="J324"/>
@@ -7604,7 +7445,7 @@
         <v>45565</v>
       </c>
       <c r="B325" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C325"/>
       <c r="D325"/>
@@ -7612,7 +7453,7 @@
       <c r="F325"/>
       <c r="G325"/>
       <c r="H325" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="I325"/>
       <c r="J325"/>
@@ -7623,7 +7464,7 @@
         <v>45596</v>
       </c>
       <c r="B326" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C326"/>
       <c r="D326"/>
@@ -7631,7 +7472,7 @@
       <c r="F326"/>
       <c r="G326"/>
       <c r="H326" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="I326"/>
       <c r="J326"/>
@@ -7642,7 +7483,7 @@
         <v>45596</v>
       </c>
       <c r="B327" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C327"/>
       <c r="D327"/>
@@ -7650,7 +7491,7 @@
       <c r="F327"/>
       <c r="G327"/>
       <c r="H327" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="I327"/>
       <c r="J327"/>
@@ -7669,7 +7510,7 @@
       <c r="F328"/>
       <c r="G328"/>
       <c r="H328" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="I328"/>
       <c r="J328"/>
@@ -7680,7 +7521,7 @@
         <v>45596</v>
       </c>
       <c r="B329" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C329"/>
       <c r="D329"/>
@@ -7688,7 +7529,7 @@
       <c r="F329"/>
       <c r="G329"/>
       <c r="H329" t="s">
-        <v>289</v>
+        <v>183</v>
       </c>
       <c r="I329"/>
       <c r="J329"/>
@@ -7699,7 +7540,7 @@
         <v>45626</v>
       </c>
       <c r="B330" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C330"/>
       <c r="D330"/>
@@ -7707,7 +7548,7 @@
       <c r="F330"/>
       <c r="G330"/>
       <c r="H330" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="I330"/>
       <c r="J330"/>
@@ -7726,7 +7567,7 @@
       <c r="F331"/>
       <c r="G331"/>
       <c r="H331" t="s">
-        <v>291</v>
+        <v>116</v>
       </c>
       <c r="I331"/>
       <c r="J331"/>
@@ -7737,7 +7578,7 @@
         <v>45626</v>
       </c>
       <c r="B332" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C332"/>
       <c r="D332"/>
@@ -7745,7 +7586,7 @@
       <c r="F332"/>
       <c r="G332"/>
       <c r="H332" t="s">
-        <v>292</v>
+        <v>150</v>
       </c>
       <c r="I332"/>
       <c r="J332"/>
@@ -7756,7 +7597,7 @@
         <v>45626</v>
       </c>
       <c r="B333" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C333"/>
       <c r="D333"/>
@@ -7764,7 +7605,7 @@
       <c r="F333"/>
       <c r="G333"/>
       <c r="H333" t="s">
-        <v>71</v>
+        <v>260</v>
       </c>
       <c r="I333"/>
       <c r="J333"/>
@@ -7775,7 +7616,7 @@
         <v>45657</v>
       </c>
       <c r="B334" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C334"/>
       <c r="D334"/>
@@ -7783,7 +7624,7 @@
       <c r="F334"/>
       <c r="G334"/>
       <c r="H334" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="I334"/>
       <c r="J334"/>
@@ -7794,7 +7635,7 @@
         <v>45657</v>
       </c>
       <c r="B335" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C335"/>
       <c r="D335"/>
@@ -7802,7 +7643,7 @@
       <c r="F335"/>
       <c r="G335"/>
       <c r="H335" t="s">
-        <v>294</v>
+        <v>96</v>
       </c>
       <c r="I335"/>
       <c r="J335"/>
@@ -7813,7 +7654,7 @@
         <v>45657</v>
       </c>
       <c r="B336" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C336"/>
       <c r="D336"/>
@@ -7821,7 +7662,7 @@
       <c r="F336"/>
       <c r="G336"/>
       <c r="H336" t="s">
-        <v>128</v>
+        <v>262</v>
       </c>
       <c r="I336"/>
       <c r="J336"/>
@@ -7832,7 +7673,7 @@
         <v>45657</v>
       </c>
       <c r="B337" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C337"/>
       <c r="D337"/>
@@ -7840,7 +7681,7 @@
       <c r="F337"/>
       <c r="G337"/>
       <c r="H337" t="s">
-        <v>295</v>
+        <v>33</v>
       </c>
       <c r="I337"/>
       <c r="J337"/>
@@ -7851,7 +7692,7 @@
         <v>45688</v>
       </c>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C338"/>
       <c r="D338"/>
@@ -7859,7 +7700,7 @@
       <c r="F338"/>
       <c r="G338"/>
       <c r="H338" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="I338"/>
       <c r="J338"/>
@@ -7870,7 +7711,7 @@
         <v>45688</v>
       </c>
       <c r="B339" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C339"/>
       <c r="D339"/>
@@ -7878,7 +7719,7 @@
       <c r="F339"/>
       <c r="G339"/>
       <c r="H339" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="I339"/>
       <c r="J339"/>
@@ -7889,7 +7730,7 @@
         <v>45688</v>
       </c>
       <c r="B340" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C340"/>
       <c r="D340"/>
@@ -7897,7 +7738,7 @@
       <c r="F340"/>
       <c r="G340"/>
       <c r="H340" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="I340"/>
       <c r="J340"/>
@@ -7908,7 +7749,7 @@
         <v>45688</v>
       </c>
       <c r="B341" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C341"/>
       <c r="D341"/>
@@ -7916,7 +7757,7 @@
       <c r="F341"/>
       <c r="G341"/>
       <c r="H341" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="I341"/>
       <c r="J341"/>
@@ -7935,7 +7776,7 @@
       <c r="F342"/>
       <c r="G342"/>
       <c r="H342" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="I342"/>
       <c r="J342"/>
@@ -7946,7 +7787,7 @@
         <v>45716</v>
       </c>
       <c r="B343" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C343"/>
       <c r="D343"/>
@@ -7954,7 +7795,7 @@
       <c r="F343"/>
       <c r="G343"/>
       <c r="H343" t="s">
-        <v>301</v>
+        <v>197</v>
       </c>
       <c r="I343"/>
       <c r="J343"/>
@@ -7973,7 +7814,7 @@
       <c r="F344"/>
       <c r="G344"/>
       <c r="H344" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="I344"/>
       <c r="J344"/>
@@ -7984,7 +7825,7 @@
         <v>45716</v>
       </c>
       <c r="B345" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C345"/>
       <c r="D345"/>
@@ -7992,7 +7833,7 @@
       <c r="F345"/>
       <c r="G345"/>
       <c r="H345" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
       <c r="I345"/>
       <c r="J345"/>
@@ -8003,7 +7844,7 @@
         <v>45747</v>
       </c>
       <c r="B346" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C346"/>
       <c r="D346"/>
@@ -8011,7 +7852,7 @@
       <c r="F346"/>
       <c r="G346"/>
       <c r="H346" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="I346"/>
       <c r="J346"/>
@@ -8030,7 +7871,7 @@
       <c r="F347"/>
       <c r="G347"/>
       <c r="H347" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="I347"/>
       <c r="J347"/>
@@ -8041,7 +7882,7 @@
         <v>45747</v>
       </c>
       <c r="B348" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C348"/>
       <c r="D348"/>
@@ -8049,7 +7890,7 @@
       <c r="F348"/>
       <c r="G348"/>
       <c r="H348" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="I348"/>
       <c r="J348"/>
@@ -8060,7 +7901,7 @@
         <v>45747</v>
       </c>
       <c r="B349" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C349"/>
       <c r="D349"/>
@@ -8068,7 +7909,7 @@
       <c r="F349"/>
       <c r="G349"/>
       <c r="H349" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="I349"/>
       <c r="J349"/>
@@ -8079,7 +7920,7 @@
         <v>45777</v>
       </c>
       <c r="B350" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C350"/>
       <c r="D350"/>
@@ -8087,7 +7928,7 @@
       <c r="F350"/>
       <c r="G350"/>
       <c r="H350" t="s">
-        <v>306</v>
+        <v>152</v>
       </c>
       <c r="I350"/>
       <c r="J350"/>
@@ -8098,7 +7939,7 @@
         <v>45777</v>
       </c>
       <c r="B351" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C351"/>
       <c r="D351"/>
@@ -8106,7 +7947,7 @@
       <c r="F351"/>
       <c r="G351"/>
       <c r="H351" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="I351"/>
       <c r="J351"/>
@@ -8117,7 +7958,7 @@
         <v>45777</v>
       </c>
       <c r="B352" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C352"/>
       <c r="D352"/>
@@ -8125,7 +7966,7 @@
       <c r="F352"/>
       <c r="G352"/>
       <c r="H352" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="I352"/>
       <c r="J352"/>
@@ -8136,7 +7977,7 @@
         <v>45777</v>
       </c>
       <c r="B353" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C353"/>
       <c r="D353"/>
@@ -8144,7 +7985,7 @@
       <c r="F353"/>
       <c r="G353"/>
       <c r="H353" t="s">
-        <v>308</v>
+        <v>126</v>
       </c>
       <c r="I353"/>
       <c r="J353"/>
@@ -8155,7 +7996,7 @@
         <v>45808</v>
       </c>
       <c r="B354" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C354"/>
       <c r="D354"/>
@@ -8163,7 +8004,7 @@
       <c r="F354"/>
       <c r="G354"/>
       <c r="H354" t="s">
-        <v>309</v>
+        <v>45</v>
       </c>
       <c r="I354"/>
       <c r="J354"/>
@@ -8174,7 +8015,7 @@
         <v>45808</v>
       </c>
       <c r="B355" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C355"/>
       <c r="D355"/>
@@ -8182,7 +8023,7 @@
       <c r="F355"/>
       <c r="G355"/>
       <c r="H355" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="I355"/>
       <c r="J355"/>
@@ -8201,7 +8042,7 @@
       <c r="F356"/>
       <c r="G356"/>
       <c r="H356" t="s">
-        <v>310</v>
+        <v>233</v>
       </c>
       <c r="I356"/>
       <c r="J356"/>
@@ -8212,7 +8053,7 @@
         <v>45808</v>
       </c>
       <c r="B357" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C357"/>
       <c r="D357"/>
@@ -8220,7 +8061,7 @@
       <c r="F357"/>
       <c r="G357"/>
       <c r="H357" t="s">
-        <v>311</v>
+        <v>167</v>
       </c>
       <c r="I357"/>
       <c r="J357"/>
@@ -8231,7 +8072,7 @@
         <v>45838</v>
       </c>
       <c r="B358" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C358"/>
       <c r="D358"/>
@@ -8239,7 +8080,7 @@
       <c r="F358"/>
       <c r="G358"/>
       <c r="H358" t="s">
-        <v>312</v>
+        <v>56</v>
       </c>
       <c r="I358"/>
       <c r="J358"/>
@@ -8250,7 +8091,7 @@
         <v>45838</v>
       </c>
       <c r="B359" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C359"/>
       <c r="D359"/>
@@ -8258,7 +8099,7 @@
       <c r="F359"/>
       <c r="G359"/>
       <c r="H359" t="s">
-        <v>313</v>
+        <v>274</v>
       </c>
       <c r="I359"/>
       <c r="J359"/>
@@ -8277,7 +8118,7 @@
       <c r="F360"/>
       <c r="G360"/>
       <c r="H360" t="s">
-        <v>314</v>
+        <v>195</v>
       </c>
       <c r="I360"/>
       <c r="J360"/>
@@ -8288,7 +8129,7 @@
         <v>45838</v>
       </c>
       <c r="B361" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C361"/>
       <c r="D361"/>
@@ -8296,7 +8137,7 @@
       <c r="F361"/>
       <c r="G361"/>
       <c r="H361" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="I361"/>
       <c r="J361"/>
@@ -8307,7 +8148,7 @@
         <v>45869</v>
       </c>
       <c r="B362" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C362"/>
       <c r="D362"/>
@@ -8315,7 +8156,7 @@
       <c r="F362"/>
       <c r="G362"/>
       <c r="H362" t="s">
-        <v>316</v>
+        <v>86</v>
       </c>
       <c r="I362"/>
       <c r="J362"/>
@@ -8334,7 +8175,7 @@
       <c r="F363"/>
       <c r="G363"/>
       <c r="H363" t="s">
-        <v>317</v>
+        <v>72</v>
       </c>
       <c r="I363"/>
       <c r="J363"/>
@@ -8353,7 +8194,7 @@
       <c r="F364"/>
       <c r="G364"/>
       <c r="H364" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
       <c r="I364"/>
       <c r="J364"/>
@@ -8364,7 +8205,7 @@
         <v>45869</v>
       </c>
       <c r="B365" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C365"/>
       <c r="D365"/>
@@ -8372,7 +8213,7 @@
       <c r="F365"/>
       <c r="G365"/>
       <c r="H365" t="s">
-        <v>128</v>
+        <v>277</v>
       </c>
       <c r="I365"/>
       <c r="J365"/>
@@ -8383,7 +8224,7 @@
         <v>45900</v>
       </c>
       <c r="B366" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C366"/>
       <c r="D366"/>
@@ -8391,7 +8232,7 @@
       <c r="F366"/>
       <c r="G366"/>
       <c r="H366" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="I366"/>
       <c r="J366"/>
@@ -8402,7 +8243,7 @@
         <v>45900</v>
       </c>
       <c r="B367" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C367"/>
       <c r="D367"/>
@@ -8410,7 +8251,7 @@
       <c r="F367"/>
       <c r="G367"/>
       <c r="H367" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
       <c r="I367"/>
       <c r="J367"/>
@@ -8421,7 +8262,7 @@
         <v>45900</v>
       </c>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C368"/>
       <c r="D368"/>
@@ -8429,7 +8270,7 @@
       <c r="F368"/>
       <c r="G368"/>
       <c r="H368" t="s">
-        <v>321</v>
+        <v>174</v>
       </c>
       <c r="I368"/>
       <c r="J368"/>
@@ -8440,7 +8281,7 @@
         <v>45900</v>
       </c>
       <c r="B369" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C369"/>
       <c r="D369"/>
@@ -8448,7 +8289,7 @@
       <c r="F369"/>
       <c r="G369"/>
       <c r="H369" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="I369"/>
       <c r="J369"/>
@@ -8459,7 +8300,7 @@
         <v>45930</v>
       </c>
       <c r="B370" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C370"/>
       <c r="D370"/>
@@ -8467,7 +8308,7 @@
       <c r="F370"/>
       <c r="G370"/>
       <c r="H370" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="I370"/>
       <c r="J370"/>
@@ -8478,7 +8319,7 @@
         <v>45930</v>
       </c>
       <c r="B371" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C371"/>
       <c r="D371"/>
@@ -8486,7 +8327,7 @@
       <c r="F371"/>
       <c r="G371"/>
       <c r="H371" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="I371"/>
       <c r="J371"/>
@@ -8497,7 +8338,7 @@
         <v>45930</v>
       </c>
       <c r="B372" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C372"/>
       <c r="D372"/>
@@ -8505,7 +8346,7 @@
       <c r="F372"/>
       <c r="G372"/>
       <c r="H372" t="s">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="I372"/>
       <c r="J372"/>
@@ -8516,7 +8357,7 @@
         <v>45930</v>
       </c>
       <c r="B373" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C373"/>
       <c r="D373"/>
@@ -8524,7 +8365,7 @@
       <c r="F373"/>
       <c r="G373"/>
       <c r="H373" t="s">
-        <v>325</v>
+        <v>280</v>
       </c>
       <c r="I373"/>
       <c r="J373"/>
@@ -8543,7 +8384,7 @@
       <c r="F374"/>
       <c r="G374"/>
       <c r="H374" t="s">
-        <v>165</v>
+        <v>282</v>
       </c>
       <c r="I374"/>
       <c r="J374"/>
@@ -8554,7 +8395,7 @@
         <v>45961</v>
       </c>
       <c r="B375" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C375"/>
       <c r="D375"/>
@@ -8562,7 +8403,7 @@
       <c r="F375"/>
       <c r="G375"/>
       <c r="H375" t="s">
-        <v>326</v>
+        <v>143</v>
       </c>
       <c r="I375"/>
       <c r="J375"/>
@@ -8581,7 +8422,7 @@
       <c r="F376"/>
       <c r="G376"/>
       <c r="H376" t="s">
-        <v>327</v>
+        <v>283</v>
       </c>
       <c r="I376"/>
       <c r="J376"/>
@@ -8592,7 +8433,7 @@
         <v>45961</v>
       </c>
       <c r="B377" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C377"/>
       <c r="D377"/>
@@ -8600,7 +8441,7 @@
       <c r="F377"/>
       <c r="G377"/>
       <c r="H377" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="I377"/>
       <c r="J377"/>
@@ -8619,7 +8460,7 @@
       <c r="F378"/>
       <c r="G378"/>
       <c r="H378" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="I378"/>
       <c r="J378"/>
@@ -8630,7 +8471,7 @@
         <v>45991</v>
       </c>
       <c r="B379" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C379"/>
       <c r="D379"/>
@@ -8638,7 +8479,7 @@
       <c r="F379"/>
       <c r="G379"/>
       <c r="H379" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="I379"/>
       <c r="J379"/>
@@ -8649,7 +8490,7 @@
         <v>45991</v>
       </c>
       <c r="B380" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C380"/>
       <c r="D380"/>
@@ -8657,7 +8498,7 @@
       <c r="F380"/>
       <c r="G380"/>
       <c r="H380" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="I380"/>
       <c r="J380"/>
@@ -8668,7 +8509,7 @@
         <v>45991</v>
       </c>
       <c r="B381" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C381"/>
       <c r="D381"/>
@@ -8676,7 +8517,7 @@
       <c r="F381"/>
       <c r="G381"/>
       <c r="H381" t="s">
-        <v>331</v>
+        <v>72</v>
       </c>
       <c r="I381"/>
       <c r="J381"/>
@@ -8687,7 +8528,7 @@
         <v>46022</v>
       </c>
       <c r="B382" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C382"/>
       <c r="D382"/>
@@ -8695,7 +8536,7 @@
       <c r="F382"/>
       <c r="G382"/>
       <c r="H382" t="s">
-        <v>332</v>
+        <v>204</v>
       </c>
       <c r="I382"/>
       <c r="J382"/>
@@ -8706,7 +8547,7 @@
         <v>46022</v>
       </c>
       <c r="B383" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C383"/>
       <c r="D383"/>
@@ -8714,7 +8555,7 @@
       <c r="F383"/>
       <c r="G383"/>
       <c r="H383" t="s">
-        <v>32</v>
+        <v>287</v>
       </c>
       <c r="I383"/>
       <c r="J383"/>
@@ -8725,7 +8566,7 @@
         <v>46022</v>
       </c>
       <c r="B384" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C384"/>
       <c r="D384"/>
@@ -8733,7 +8574,7 @@
       <c r="F384"/>
       <c r="G384"/>
       <c r="H384" t="s">
-        <v>333</v>
+        <v>105</v>
       </c>
       <c r="I384"/>
       <c r="J384"/>
@@ -8744,7 +8585,7 @@
         <v>46022</v>
       </c>
       <c r="B385" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C385"/>
       <c r="D385"/>
@@ -8752,7 +8593,7 @@
       <c r="F385"/>
       <c r="G385"/>
       <c r="H385" t="s">
-        <v>334</v>
+        <v>37</v>
       </c>
       <c r="I385"/>
       <c r="J385"/>
@@ -8771,7 +8612,7 @@
       <c r="F386"/>
       <c r="G386"/>
       <c r="H386" t="s">
-        <v>335</v>
+        <v>288</v>
       </c>
       <c r="I386"/>
       <c r="J386"/>
@@ -8790,7 +8631,7 @@
       <c r="F387"/>
       <c r="G387"/>
       <c r="H387" t="s">
-        <v>336</v>
+        <v>100</v>
       </c>
       <c r="I387"/>
       <c r="J387"/>
@@ -8801,7 +8642,7 @@
         <v>46053</v>
       </c>
       <c r="B388" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C388"/>
       <c r="D388"/>
@@ -8809,7 +8650,7 @@
       <c r="F388"/>
       <c r="G388"/>
       <c r="H388" t="s">
-        <v>337</v>
+        <v>145</v>
       </c>
       <c r="I388"/>
       <c r="J388"/>
@@ -8820,7 +8661,7 @@
         <v>46053</v>
       </c>
       <c r="B389" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C389"/>
       <c r="D389"/>
@@ -8828,7 +8669,7 @@
       <c r="F389"/>
       <c r="G389"/>
       <c r="H389" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="I389"/>
       <c r="J389"/>
@@ -8839,7 +8680,7 @@
         <v>46081</v>
       </c>
       <c r="B390" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C390"/>
       <c r="D390"/>
@@ -8847,7 +8688,7 @@
       <c r="F390"/>
       <c r="G390"/>
       <c r="H390" t="s">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="I390"/>
       <c r="J390"/>
@@ -8858,7 +8699,7 @@
         <v>46081</v>
       </c>
       <c r="B391" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C391"/>
       <c r="D391"/>
@@ -8866,7 +8707,7 @@
       <c r="F391"/>
       <c r="G391"/>
       <c r="H391" t="s">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="I391"/>
       <c r="J391"/>
@@ -8877,7 +8718,7 @@
         <v>46081</v>
       </c>
       <c r="B392" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C392"/>
       <c r="D392"/>
@@ -8885,7 +8726,7 @@
       <c r="F392"/>
       <c r="G392"/>
       <c r="H392" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="I392"/>
       <c r="J392"/>
@@ -8896,7 +8737,7 @@
         <v>46081</v>
       </c>
       <c r="B393" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C393"/>
       <c r="D393"/>
@@ -8904,7 +8745,7 @@
       <c r="F393"/>
       <c r="G393"/>
       <c r="H393" t="s">
-        <v>341</v>
+        <v>291</v>
       </c>
       <c r="I393"/>
       <c r="J393"/>
@@ -8915,7 +8756,7 @@
         <v>46112</v>
       </c>
       <c r="B394" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C394"/>
       <c r="D394"/>
@@ -8923,7 +8764,7 @@
       <c r="F394"/>
       <c r="G394"/>
       <c r="H394" t="s">
-        <v>342</v>
+        <v>203</v>
       </c>
       <c r="I394"/>
       <c r="J394"/>
@@ -8942,7 +8783,7 @@
       <c r="F395"/>
       <c r="G395"/>
       <c r="H395" t="s">
-        <v>61</v>
+        <v>292</v>
       </c>
       <c r="I395"/>
       <c r="J395"/>
@@ -8953,7 +8794,7 @@
         <v>46112</v>
       </c>
       <c r="B396" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C396"/>
       <c r="D396"/>
@@ -8961,7 +8802,7 @@
       <c r="F396"/>
       <c r="G396"/>
       <c r="H396" t="s">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="I396"/>
       <c r="J396"/>
@@ -8972,7 +8813,7 @@
         <v>46112</v>
       </c>
       <c r="B397" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C397"/>
       <c r="D397"/>
@@ -8980,7 +8821,7 @@
       <c r="F397"/>
       <c r="G397"/>
       <c r="H397" t="s">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="I397"/>
       <c r="J397"/>
@@ -8991,7 +8832,7 @@
         <v>46142</v>
       </c>
       <c r="B398" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C398"/>
       <c r="D398"/>
@@ -8999,7 +8840,7 @@
       <c r="F398"/>
       <c r="G398"/>
       <c r="H398" t="s">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="I398"/>
       <c r="J398"/>
@@ -9018,7 +8859,7 @@
       <c r="F399"/>
       <c r="G399"/>
       <c r="H399" t="s">
-        <v>346</v>
+        <v>74</v>
       </c>
       <c r="I399"/>
       <c r="J399"/>
@@ -9029,7 +8870,7 @@
         <v>46142</v>
       </c>
       <c r="B400" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C400"/>
       <c r="D400"/>
@@ -9037,7 +8878,7 @@
       <c r="F400"/>
       <c r="G400"/>
       <c r="H400" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="I400"/>
       <c r="J400"/>
@@ -9056,7 +8897,7 @@
       <c r="F401"/>
       <c r="G401"/>
       <c r="H401" t="s">
-        <v>348</v>
+        <v>295</v>
       </c>
       <c r="I401"/>
       <c r="J401"/>
